--- a/VerveStacks_VNM_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_VNM_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60FE7A6B-0FA4-4615-AED2-BDB4AE07B3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD3215D0-7BC3-4C45-BDF4-FF56966E7B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -886,232 +886,322 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_015</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_VN321-220,e_w1267181647-220,e_VN297-500,e_VN128-500,e_VN324-500,e_VN322-220,e_VN314-500,e_VN256-220,e_w1320784083-500,e_VN320-220,e_VN312-220,e_w1036283936-220,e_w750907640-220</t>
+  </si>
+  <si>
+    <t>e_VN3-220,e_w1240393348-220</t>
+  </si>
+  <si>
+    <t>e_VN738-500,e_w549380074-220,e_w401532710-220,e_VN624-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN644-500</t>
+  </si>
+  <si>
+    <t>e_w1050835279-220,e_VN278-500,e_VN235-500,e_VN321-220,e_w857794232-220,e_VN280-500</t>
+  </si>
+  <si>
+    <t>e_w439941742-220,e_VN556-500,e_VN512-500,e_w401042494-220,e_w1233471417-220,e_VN585-500,e_VN537-220,e_VN522-500,e_w1258175914-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>e_VN39-500,e_VN27-500,e_VN60-500,e_w1337952924-220,e_VN62-500,e_VN22-220</t>
+  </si>
+  <si>
+    <t>e_VN117-500,e_w1263497522-220,e_w1263839745-220,e_w481965040-220,e_VN122-500,e_VN23-220,e_VN11-220</t>
+  </si>
+  <si>
+    <t>e_w1050835279-220,e_VN352-220,e_VN366-500,e_VN345-220</t>
+  </si>
+  <si>
+    <t>e_VN1152-220,e_w548752026-220,e_VN1099-500,e_w1273948690-220,e_w1273948701-220,e_w1273898576-220,e_w400474243-220,e_VN988-220,e_w1273527149-220</t>
+  </si>
+  <si>
+    <t>e_VN8-500,e_w893223532-220,e_VN16-500,e_VN15-500,e_w1263573984-220,e_VN2-220</t>
+  </si>
+  <si>
+    <t>e_VN367-500,e_VN384-500,e_VN374-500,e_VN447-500,e_VN433-500</t>
+  </si>
+  <si>
+    <t>e_w548970103-220,e_w548970101-220,e_VN1227-220,e_VN1207-500,e_w549005377-220,e_VN1210-500,e_w827889600-220,e_w1052065872-220,e_w744217936-220</t>
+  </si>
+  <si>
+    <t>e_VN900-500,e_VN855-500,e_w1273328710-220,e_VN1013-220,e_VN907-220,e_VN832-500,e_w400413521-220,e_w400482074-220,e_VN920-500,e_VN816-500</t>
+  </si>
+  <si>
+    <t>e_VN310-220,e_w1045125739-220,e_VN152-500,e_w469414362-220,e_w241065371-220,e_VN167-220,e_w827889590-500,e_w1245195233-220</t>
+  </si>
+  <si>
+    <t>e_VN614-220,e_VN590-220,e_VN611-500,e_VN728-220,e_VN695-220,e_VN648-500,e_VN702-220,e_VN623-500,e_w1272088369-220</t>
+  </si>
+  <si>
+    <t>e_VN390-500,e_VN375-220,e_VN457-500,e_VN441-500,e_w630750798-500</t>
+  </si>
+  <si>
+    <t>e_VN1130-500,e_w1051605925-220,e_w775832889-220,e_VN1156-500,e_w1052403240-220,e_VN983-220,e_w1176845159-220,e_VN1154-220,e_VN1097-220,e_VN987-500,e_VN930-500,e_VN918-500,e_w1212041269-220,e_VN1017-500</t>
+  </si>
+  <si>
+    <t>e_VN1206-220,e_VN1186-220,e_w548970103-220,e_w548970109-220,e_VN1188-220,e_w967849373-220,e_VN1227-220,e_w548970118-220,e_w548869165-230,e_w548869165-220,e_w773079147-220,e_VN1164-500</t>
+  </si>
+  <si>
+    <t>e_VN4-220,e_VN3-220,e_w1240393348-220</t>
+  </si>
+  <si>
+    <t>e_w715041211-220</t>
+  </si>
+  <si>
+    <t>e_VN770-500,e_VN748-500,e_VN844-500,e_VN753-220,e_VN714-220,e_VN836-220,e_w1273255944-220,e_w549197475-220,e_w549296358-220</t>
+  </si>
+  <si>
     <t>e_w1264568817-220,e_w1264568832-220,e_VN132-220,e_w483057097-220,e_VN12-220,e_VN118-500,e_w1240467340-220</t>
   </si>
   <si>
     <t>e_VN477-500,e_VN464-500,e_VN484-500,e_VN476-500,e_VN467-500,e_VN569-220,e_VN510-220,e_VN488-220,e_VN471-500</t>
   </si>
   <si>
-    <t>e_VN310-220,e_w1045125739-220,e_VN152-500,e_w469414362-220,e_w241065371-220,e_VN167-220,e_w827889590-500,e_w1245195233-220</t>
-  </si>
-  <si>
-    <t>e_VN614-220,e_VN590-220,e_VN611-500,e_VN728-220,e_VN695-220,e_VN648-500,e_VN702-220,e_VN623-500,e_w1272088369-220</t>
-  </si>
-  <si>
-    <t>e_VN390-500,e_VN375-220,e_VN457-500,e_VN441-500,e_w630750798-500</t>
-  </si>
-  <si>
-    <t>e_VN39-500,e_VN27-500,e_VN60-500,e_w1337952924-220,e_VN62-500,e_VN22-220</t>
-  </si>
-  <si>
-    <t>e_VN117-500,e_w1263497522-220,e_w1263839745-220,e_w481965040-220,e_VN122-500,e_VN23-220,e_VN11-220</t>
-  </si>
-  <si>
-    <t>e_w1050835279-220,e_VN352-220,e_VN366-500,e_VN345-220</t>
-  </si>
-  <si>
-    <t>e_VN1152-220,e_w548752026-220,e_VN1099-500,e_w1273948690-220,e_w1273948701-220,e_w1273898576-220,e_w400474243-220,e_VN988-220,e_w1273527149-220</t>
-  </si>
-  <si>
-    <t>e_VN321-220,e_w1267181647-220,e_VN297-500,e_VN128-500,e_VN324-500,e_VN322-220,e_VN314-500,e_VN256-220,e_w1320784083-500,e_VN320-220,e_VN312-220,e_w1036283936-220,e_w750907640-220</t>
-  </si>
-  <si>
-    <t>e_VN3-220,e_w1240393348-220</t>
-  </si>
-  <si>
-    <t>e_VN738-500,e_w549380074-220,e_w401532710-220,e_VN624-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN644-500</t>
-  </si>
-  <si>
-    <t>e_VN8-500,e_w893223532-220,e_VN16-500,e_VN15-500,e_w1263573984-220,e_VN2-220</t>
-  </si>
-  <si>
-    <t>e_VN367-500,e_VN384-500,e_VN374-500,e_VN447-500,e_VN433-500</t>
-  </si>
-  <si>
-    <t>e_VN1206-220,e_VN1186-220,e_w548970103-220,e_w548970109-220,e_VN1188-220,e_w967849373-220,e_VN1227-220,e_w548970118-220,e_w548869165-230,e_w548869165-220,e_w773079147-220,e_VN1164-500</t>
-  </si>
-  <si>
-    <t>e_VN4-220,e_VN3-220,e_w1240393348-220</t>
-  </si>
-  <si>
-    <t>e_w715041211-220</t>
-  </si>
-  <si>
-    <t>e_VN770-500,e_VN748-500,e_VN844-500,e_VN753-220,e_VN714-220,e_VN836-220,e_w1273255944-220,e_w549197475-220,e_w549296358-220</t>
-  </si>
-  <si>
     <t>e_w1050835279-220,e_VN351-220</t>
   </si>
   <si>
-    <t>e_w548970103-220,e_w548970101-220,e_VN1227-220,e_VN1207-500,e_w549005377-220,e_VN1210-500,e_w827889600-220,e_w1052065872-220,e_w744217936-220</t>
-  </si>
-  <si>
-    <t>e_VN900-500,e_VN855-500,e_w1273328710-220,e_VN1013-220,e_VN907-220,e_VN832-500,e_w400413521-220,e_w400482074-220,e_VN920-500,e_VN816-500</t>
-  </si>
-  <si>
-    <t>e_w1050835279-220,e_VN278-500,e_VN235-500,e_VN321-220,e_w857794232-220,e_VN280-500</t>
-  </si>
-  <si>
-    <t>e_w439941742-220,e_VN556-500,e_VN512-500,e_w401042494-220,e_w1233471417-220,e_VN585-500,e_VN537-220,e_VN522-500,e_w1258175914-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>e_VN1130-500,e_w1051605925-220,e_w775832889-220,e_VN1156-500,e_w1052403240-220,e_VN983-220,e_w1176845159-220,e_VN1154-220,e_VN1097-220,e_VN987-500,e_VN930-500,e_VN918-500,e_w1212041269-220,e_VN1017-500</t>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_010</t>
@@ -1120,100 +1210,100 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_006</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_VN1156-500,e_VN1154-220,e_VN1152-220</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_VN648-500,e_VN753-220,e_VN714-220,e_VN702-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_VN345-220,e_VN324-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w1273328710-220,e_VN738-500,e_w549380074-220,e_VN832-500,e_w400413521-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN770-500,e_VN748-500,e_VN728-220,e_VN695-220,e_w1273898576-220,e_w400474243-220,e_VN988-220,e_w1273527149-220</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_VN384-500,e_VN447-500,e_VN433-500,e_VN477-500,e_VN464-500,e_VN457-500,e_VN484-500,e_VN476-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_VN1206-220,e_VN1186-220,e_w548970109-220,e_VN1188-220</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w1240393348-220</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_VN623-500,e_w1258175914-220,e_w1272088369-220</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w1320784083-500,e_VN320-220,e_VN312-220,e_w750907640-220,e_VN310-220,e_w1045125739-220,e_w241065371-220,e_w715041211-220,e_w1245195233-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_VN1206-220,e_w548970103-220,e_VN1227-220,e_w548970118-220,e_VN1207-500,e_VN1210-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_VN537-220,e_VN522-500,e_w549400051-220,e_VN575-220</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_VN488-220,e_VN471-500,e_VN512-500,e_w401042494-220</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w548970103-220,e_w548970101-220,e_w549005377-220,e_w827889600-220,e_w1052065872-220,e_w744217936-220,e_w548752026-220,e_VN1099-500,e_w1273948690-220,e_w400482074-220,e_w1273948701-220</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_VN374-500,e_VN390-500,e_VN375-220,e_VN441-500,e_w630750798-500,e_VN467-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w1036283936-220,e_VN118-500,e_w483057097-220,e_VN152-500,e_w469414362-220,e_VN3-220,e_VN167-220,e_w1240393348-220,e_w827889590-500,e_w1245195233-220</t>
   </si>
   <si>
     <t>elc_won_010</t>
@@ -1222,100 +1312,40 @@
     <t>e_w775832889-220,e_VN918-500,e_VN900-500,e_VN855-500</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w548970103-220,e_w548970101-220,e_w549005377-220,e_w827889600-220,e_w1052065872-220,e_w744217936-220,e_w548752026-220,e_VN1099-500,e_w1273948690-220,e_w400482074-220,e_w1273948701-220</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_VN384-500,e_VN447-500,e_VN433-500,e_VN477-500,e_VN464-500,e_VN457-500,e_VN484-500,e_VN476-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w1320784083-500,e_VN320-220,e_VN312-220,e_w750907640-220,e_VN310-220,e_w1045125739-220,e_w241065371-220,e_w715041211-220,e_w1245195233-220</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_VN488-220,e_VN471-500,e_VN512-500,e_w401042494-220</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_VN1206-220,e_w548970103-220,e_VN1227-220,e_w548970118-220,e_VN1207-500,e_VN1210-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_VN537-220,e_VN522-500,e_w549400051-220,e_VN575-220</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w1036283936-220,e_VN118-500,e_w483057097-220,e_VN152-500,e_w469414362-220,e_VN3-220,e_VN167-220,e_w1240393348-220,e_w827889590-500,e_w1245195233-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_VN648-500,e_VN753-220,e_VN714-220,e_VN702-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_VN1156-500,e_VN1154-220,e_VN1152-220</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_VN1206-220,e_VN1186-220,e_w548970109-220,e_VN1188-220</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w1240393348-220</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_VN623-500,e_w1258175914-220,e_w1272088369-220</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_VN345-220,e_VN324-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w1273328710-220,e_VN738-500,e_w549380074-220,e_VN832-500,e_w400413521-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN770-500,e_VN748-500,e_VN728-220,e_VN695-220,e_w1273898576-220,e_w400474243-220,e_VN988-220,e_w1273527149-220</t>
-  </si>
-  <si>
     <t>elc_won_006</t>
   </si>
   <si>
     <t>e_w967849373-220,e_w548869165-230,e_w548869165-220,e_w773079147-220,e_VN1164-500,e_VN1130-500</t>
   </si>
   <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_VN374-500,e_VN390-500,e_VN375-220,e_VN441-500,e_w630750798-500,e_VN467-500</t>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wofelc_wof_015</t>
@@ -1348,6 +1378,30 @@
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_001</t>
   </si>
   <si>
@@ -1360,10 +1414,28 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_002</t>
@@ -1378,76 +1450,34 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_VN446-500,e_VN410-220,e_VN468-500,e_w1087113517-220,e_w1183902227-500</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_VN1228-220,e_w548752026-220,e_w548723124-220,e_w1273948701-220,e_w548717060-500,e_VN1003-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w1273527149-220,e_VN836-220,e_w1273255946-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220,e_w1376430795-500</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_w1272088369-220,e_w1258175914-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w548970101-220,e_w827889600-500</t>
   </si>
   <si>
     <t>elc_wof_015</t>
@@ -1480,6 +1510,30 @@
     <t>e_w630750798-220,e_w1320784083-500,e_VN410-220,e_w630750798-500,e_w1183902227-500</t>
   </si>
   <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_w1272088369-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_VN1003-500,e_VN999-500,e_VN988-220,e_w1091686589-220</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w827889600-500,e_VN1228-220,e_VN1145-220</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>e_w436002389-220,e_VN470-500,e_w1183902227-500,e_w401042494-220,e_VN471-500,e_w1087113517-220,e_VN516-500</t>
+  </si>
+  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
@@ -1492,10 +1546,28 @@
     <t>e_VN516-500,e_w1374565925-220</t>
   </si>
   <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w548970101-220,e_w827889600-500</t>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_VN994-500,e_w549038673-220,e_w1274466549-220</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_w750907640-220,e_w1044469623-220,e_w715041211-220</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_w715041211-220,e_w1245195233-220</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w548970103-220,e_w548970101-220,e_w827889600-500</t>
   </si>
   <si>
     <t>elc_wof_002</t>
@@ -1505,78 +1577,6 @@
   </si>
   <si>
     <t>e_w1374565925-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_w750907640-220,e_w1044469623-220,e_w715041211-220</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_w715041211-220,e_w1245195233-220</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_VN994-500,e_w549038673-220,e_w1274466549-220</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w1272088369-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_VN1003-500,e_VN999-500,e_VN988-220,e_w1091686589-220</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_VN446-500,e_VN410-220,e_VN468-500,e_w1087113517-220,e_w1183902227-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w827889600-500,e_VN1228-220,e_VN1145-220</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_w436002389-220,e_VN470-500,e_w1183902227-500,e_w401042494-220,e_VN471-500,e_w1087113517-220,e_VN516-500</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_VN1228-220,e_w548752026-220,e_w548723124-220,e_w1273948701-220,e_w548717060-500,e_VN1003-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w1273527149-220,e_VN836-220,e_w1273255946-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220,e_w1376430795-500</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w1272088369-220,e_w1258175914-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w548970103-220,e_w548970101-220,e_w827889600-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -8274,7 +8274,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57497F43-4F70-4678-9033-65687FC2BCCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2F0FF3-5B28-4072-957E-3C7B02FDC2AD}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8512,16 +8512,16 @@
         <v>252</v>
       </c>
       <c r="Y11" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Z11" t="s">
         <v>304</v>
       </c>
       <c r="AA11">
-        <v>0.99916935310675503</v>
+        <v>0.99930751773166338</v>
       </c>
       <c r="AB11">
-        <v>15.22852637615807</v>
+        <v>12.695508252837362</v>
       </c>
       <c r="AD11" t="s">
         <v>251</v>
@@ -8554,10 +8554,10 @@
         <v>363</v>
       </c>
       <c r="AO11">
-        <v>0.9982523129285531</v>
+        <v>0.99938105508849573</v>
       </c>
       <c r="AP11">
-        <v>32.040929643194062</v>
+        <v>11.34732337757792</v>
       </c>
       <c r="AR11" t="s">
         <v>251</v>
@@ -8590,10 +8590,10 @@
         <v>441</v>
       </c>
       <c r="BC11">
-        <v>0.99497940415328234</v>
+        <v>0.99660067059502699</v>
       </c>
       <c r="BD11">
-        <v>92.044257189823469</v>
+        <v>62.321039091172274</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8658,16 +8658,16 @@
         <v>256</v>
       </c>
       <c r="Y12" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="Z12" t="s">
         <v>305</v>
       </c>
       <c r="AA12">
-        <v>0.99838245441178075</v>
+        <v>0.99544370356555212</v>
       </c>
       <c r="AB12">
-        <v>29.65500245068538</v>
+        <v>83.53210129821079</v>
       </c>
       <c r="AD12" t="s">
         <v>251</v>
@@ -8700,10 +8700,10 @@
         <v>365</v>
       </c>
       <c r="AO12">
-        <v>0.99887560286820065</v>
+        <v>0.99894245995613196</v>
       </c>
       <c r="AP12">
-        <v>20.613947416322183</v>
+        <v>19.388234137580387</v>
       </c>
       <c r="AR12" t="s">
         <v>251</v>
@@ -8736,10 +8736,10 @@
         <v>443</v>
       </c>
       <c r="BC12">
-        <v>0.99122511500292365</v>
+        <v>0.98009770506351668</v>
       </c>
       <c r="BD12">
-        <v>160.87289161306575</v>
+        <v>364.87540716886002</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8804,16 +8804,16 @@
         <v>258</v>
       </c>
       <c r="Y13" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="Z13" t="s">
         <v>306</v>
       </c>
       <c r="AA13">
-        <v>0.99853654721508034</v>
+        <v>0.99874244650354715</v>
       </c>
       <c r="AB13">
-        <v>26.829967723528117</v>
+        <v>23.055147434969136</v>
       </c>
       <c r="AD13" t="s">
         <v>251</v>
@@ -8846,10 +8846,10 @@
         <v>367</v>
       </c>
       <c r="AO13">
-        <v>0.9975164323387431</v>
+        <v>0.99926426412261371</v>
       </c>
       <c r="AP13">
-        <v>45.532073789710303</v>
+        <v>13.488491085415317</v>
       </c>
       <c r="AR13" t="s">
         <v>251</v>
@@ -8882,10 +8882,10 @@
         <v>445</v>
       </c>
       <c r="BC13">
-        <v>0.98952018191105418</v>
+        <v>0.9969294297150163</v>
       </c>
       <c r="BD13">
-        <v>192.12999829733911</v>
+        <v>56.2937885580344</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8950,16 +8950,16 @@
         <v>260</v>
       </c>
       <c r="Y14" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="Z14" t="s">
         <v>307</v>
       </c>
       <c r="AA14">
-        <v>0.99908330527279288</v>
+        <v>0.99790242535065354</v>
       </c>
       <c r="AB14">
-        <v>16.806069998796339</v>
+        <v>38.455535238019358</v>
       </c>
       <c r="AD14" t="s">
         <v>251</v>
@@ -8992,10 +8992,10 @@
         <v>369</v>
       </c>
       <c r="AO14">
-        <v>0.99898558640402924</v>
+        <v>0.99911920301541846</v>
       </c>
       <c r="AP14">
-        <v>18.597582592797586</v>
+        <v>16.147944717327473</v>
       </c>
       <c r="AR14" t="s">
         <v>251</v>
@@ -9028,10 +9028,10 @@
         <v>447</v>
       </c>
       <c r="BC14">
-        <v>0.98985969450990097</v>
+        <v>0.99534342454901092</v>
       </c>
       <c r="BD14">
-        <v>185.9056006518154</v>
+        <v>85.370549934800536</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9096,16 +9096,16 @@
         <v>262</v>
       </c>
       <c r="Y15" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="Z15" t="s">
         <v>308</v>
       </c>
       <c r="AA15">
-        <v>0.99925831158204348</v>
+        <v>0.99922833574773007</v>
       </c>
       <c r="AB15">
-        <v>13.597620995868882</v>
+        <v>14.14717795828226</v>
       </c>
       <c r="AD15" t="s">
         <v>251</v>
@@ -9138,10 +9138,10 @@
         <v>371</v>
       </c>
       <c r="AO15">
-        <v>0.99881597306370296</v>
+        <v>0.9975164323387431</v>
       </c>
       <c r="AP15">
-        <v>21.707160498778528</v>
+        <v>45.532073789710303</v>
       </c>
       <c r="AR15" t="s">
         <v>251</v>
@@ -9174,10 +9174,10 @@
         <v>449</v>
       </c>
       <c r="BC15">
-        <v>0.99345827826480626</v>
+        <v>0.97765588244922996</v>
       </c>
       <c r="BD15">
-        <v>119.93156514521847</v>
+        <v>409.64215509745077</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9284,10 +9284,10 @@
         <v>373</v>
       </c>
       <c r="AO16">
-        <v>0.99897336142834126</v>
+        <v>0.99796388855873064</v>
       </c>
       <c r="AP16">
-        <v>18.821707147077909</v>
+        <v>37.328709756605285</v>
       </c>
       <c r="AR16" t="s">
         <v>251</v>
@@ -9320,10 +9320,10 @@
         <v>451</v>
       </c>
       <c r="BC16">
-        <v>0.98389971341016413</v>
+        <v>0.99497940415328234</v>
       </c>
       <c r="BD16">
-        <v>295.17192081365857</v>
+        <v>92.044257189823469</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9430,10 +9430,10 @@
         <v>375</v>
       </c>
       <c r="AO17">
-        <v>0.99906402131845495</v>
+        <v>0.995847998099891</v>
       </c>
       <c r="AP17">
-        <v>17.15960916165827</v>
+        <v>76.120034835332021</v>
       </c>
       <c r="AR17" t="s">
         <v>251</v>
@@ -9466,10 +9466,10 @@
         <v>453</v>
       </c>
       <c r="BC17">
-        <v>0.99068186135163905</v>
+        <v>0.99122511500292365</v>
       </c>
       <c r="BD17">
-        <v>170.83254188661647</v>
+        <v>160.87289161306575</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9576,10 +9576,10 @@
         <v>377</v>
       </c>
       <c r="AO18">
-        <v>0.99766805126871516</v>
+        <v>0.99837166789655962</v>
       </c>
       <c r="AP18">
-        <v>42.752393406888629</v>
+        <v>29.852755229741184</v>
       </c>
       <c r="AR18" t="s">
         <v>251</v>
@@ -9612,10 +9612,10 @@
         <v>455</v>
       </c>
       <c r="BC18">
-        <v>0.97765588244922996</v>
+        <v>0.98952018191105418</v>
       </c>
       <c r="BD18">
-        <v>409.64215509745077</v>
+        <v>192.12999829733911</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9722,10 +9722,10 @@
         <v>379</v>
       </c>
       <c r="AO19">
-        <v>0.99894245995613196</v>
+        <v>0.99898558640402924</v>
       </c>
       <c r="AP19">
-        <v>19.388234137580387</v>
+        <v>18.597582592797586</v>
       </c>
       <c r="AR19" t="s">
         <v>251</v>
@@ -9755,13 +9755,13 @@
         <v>456</v>
       </c>
       <c r="BB19" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="BC19">
-        <v>0.98791946624258509</v>
+        <v>0.98985969450990097</v>
       </c>
       <c r="BD19">
-        <v>221.4764522192738</v>
+        <v>185.9056006518154</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9826,16 +9826,16 @@
         <v>272</v>
       </c>
       <c r="Y20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Z20" t="s">
         <v>313</v>
       </c>
       <c r="AA20">
-        <v>0.99930751773166338</v>
+        <v>0.99748113422069817</v>
       </c>
       <c r="AB20">
-        <v>12.695508252837362</v>
+        <v>46.179205953867658</v>
       </c>
       <c r="AD20" t="s">
         <v>251</v>
@@ -9868,10 +9868,10 @@
         <v>381</v>
       </c>
       <c r="AO20">
-        <v>0.99938105508849573</v>
+        <v>0.99897336142834126</v>
       </c>
       <c r="AP20">
-        <v>11.34732337757792</v>
+        <v>18.821707147077909</v>
       </c>
       <c r="AR20" t="s">
         <v>251</v>
@@ -9898,16 +9898,16 @@
         <v>414</v>
       </c>
       <c r="BA20" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BB20" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="BC20">
-        <v>0.99509603189170837</v>
+        <v>0.99345827826480626</v>
       </c>
       <c r="BD20">
-        <v>89.90608198534612</v>
+        <v>119.93156514521847</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9972,16 +9972,16 @@
         <v>274</v>
       </c>
       <c r="Y21" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="Z21" t="s">
         <v>314</v>
       </c>
       <c r="AA21">
-        <v>0.99544370356555212</v>
+        <v>0.9968034818648015</v>
       </c>
       <c r="AB21">
-        <v>83.53210129821079</v>
+        <v>58.602832478639002</v>
       </c>
       <c r="AD21" t="s">
         <v>251</v>
@@ -10014,10 +10014,10 @@
         <v>383</v>
       </c>
       <c r="AO21">
-        <v>0.99796388855873064</v>
+        <v>0.99906402131845495</v>
       </c>
       <c r="AP21">
-        <v>37.328709756605285</v>
+        <v>17.15960916165827</v>
       </c>
       <c r="AR21" t="s">
         <v>251</v>
@@ -10044,16 +10044,16 @@
         <v>416</v>
       </c>
       <c r="BA21" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="BB21" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="BC21">
-        <v>0.99160116355990502</v>
+        <v>0.98020101972536366</v>
       </c>
       <c r="BD21">
-        <v>153.97866806840764</v>
+        <v>362.98130503499954</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10118,16 +10118,16 @@
         <v>276</v>
       </c>
       <c r="Y22" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z22" t="s">
         <v>315</v>
       </c>
       <c r="AA22">
-        <v>0.99874244650354715</v>
+        <v>0.99881634769332572</v>
       </c>
       <c r="AB22">
-        <v>23.055147434969136</v>
+        <v>21.700292289029083</v>
       </c>
       <c r="AD22" t="s">
         <v>251</v>
@@ -10160,10 +10160,10 @@
         <v>385</v>
       </c>
       <c r="AO22">
-        <v>0.995847998099891</v>
+        <v>0.99881597306370296</v>
       </c>
       <c r="AP22">
-        <v>76.120034835332021</v>
+        <v>21.707160498778528</v>
       </c>
       <c r="AR22" t="s">
         <v>251</v>
@@ -10190,16 +10190,16 @@
         <v>418</v>
       </c>
       <c r="BA22" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="BB22" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BC22">
-        <v>0.99255179421932938</v>
+        <v>0.97141625641711749</v>
       </c>
       <c r="BD22">
-        <v>136.55043931229389</v>
+        <v>524.03529901951276</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10264,16 +10264,16 @@
         <v>278</v>
       </c>
       <c r="Y23" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="Z23" t="s">
         <v>316</v>
       </c>
       <c r="AA23">
-        <v>0.99748113422069817</v>
+        <v>0.99902825268538287</v>
       </c>
       <c r="AB23">
-        <v>46.179205953867658</v>
+        <v>17.815367434646582</v>
       </c>
       <c r="AD23" t="s">
         <v>251</v>
@@ -10306,10 +10306,10 @@
         <v>387</v>
       </c>
       <c r="AO23">
-        <v>0.99837166789655962</v>
+        <v>0.99887560286820065</v>
       </c>
       <c r="AP23">
-        <v>29.852755229741184</v>
+        <v>20.613947416322183</v>
       </c>
       <c r="AR23" t="s">
         <v>251</v>
@@ -10336,16 +10336,16 @@
         <v>420</v>
       </c>
       <c r="BA23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="BB23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="BC23">
-        <v>0.99560758626248369</v>
+        <v>0.98627052110774238</v>
       </c>
       <c r="BD23">
-        <v>80.527585187798735</v>
+        <v>251.70711302472259</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10410,16 +10410,16 @@
         <v>280</v>
       </c>
       <c r="Y24" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="Z24" t="s">
         <v>317</v>
       </c>
       <c r="AA24">
-        <v>0.9968034818648015</v>
+        <v>0.99853654721508034</v>
       </c>
       <c r="AB24">
-        <v>58.602832478639002</v>
+        <v>26.829967723528117</v>
       </c>
       <c r="AD24" t="s">
         <v>251</v>
@@ -10452,10 +10452,10 @@
         <v>389</v>
       </c>
       <c r="AO24">
-        <v>0.99926426412261371</v>
+        <v>0.99907918970282927</v>
       </c>
       <c r="AP24">
-        <v>13.488491085415317</v>
+        <v>16.881522114796713</v>
       </c>
       <c r="AR24" t="s">
         <v>251</v>
@@ -10482,16 +10482,16 @@
         <v>422</v>
       </c>
       <c r="BA24" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="BB24" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="BC24">
-        <v>0.98020101972536366</v>
+        <v>0.99278784076394344</v>
       </c>
       <c r="BD24">
-        <v>362.98130503499954</v>
+        <v>132.22291932770449</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10556,16 +10556,16 @@
         <v>282</v>
       </c>
       <c r="Y25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Z25" t="s">
         <v>318</v>
       </c>
       <c r="AA25">
-        <v>0.99841532396070098</v>
+        <v>0.99908330527279288</v>
       </c>
       <c r="AB25">
-        <v>29.052394053816059</v>
+        <v>16.806069998796339</v>
       </c>
       <c r="AD25" t="s">
         <v>251</v>
@@ -10598,10 +10598,10 @@
         <v>391</v>
       </c>
       <c r="AO25">
-        <v>0.99911920301541846</v>
+        <v>0.99766805126871516</v>
       </c>
       <c r="AP25">
-        <v>16.147944717327473</v>
+        <v>42.752393406888629</v>
       </c>
       <c r="AR25" t="s">
         <v>251</v>
@@ -10628,16 +10628,16 @@
         <v>424</v>
       </c>
       <c r="BA25" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="BB25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="BC25">
-        <v>0.97141625641711749</v>
+        <v>0.98389971341016413</v>
       </c>
       <c r="BD25">
-        <v>524.03529901951276</v>
+        <v>295.17192081365857</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10702,16 +10702,16 @@
         <v>284</v>
       </c>
       <c r="Y26" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="Z26" t="s">
         <v>319</v>
       </c>
       <c r="AA26">
-        <v>0.99748798960410945</v>
+        <v>0.99925831158204348</v>
       </c>
       <c r="AB26">
-        <v>46.05352392465965</v>
+        <v>13.597620995868882</v>
       </c>
       <c r="AD26" t="s">
         <v>251</v>
@@ -10744,10 +10744,10 @@
         <v>393</v>
       </c>
       <c r="AO26">
-        <v>0.99844423111858249</v>
+        <v>0.9982523129285531</v>
       </c>
       <c r="AP26">
-        <v>28.522429492654361</v>
+        <v>32.040929643194062</v>
       </c>
       <c r="AR26" t="s">
         <v>251</v>
@@ -10774,16 +10774,16 @@
         <v>426</v>
       </c>
       <c r="BA26" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="BB26" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="BC26">
-        <v>0.99660067059502699</v>
+        <v>0.99068186135163905</v>
       </c>
       <c r="BD26">
-        <v>62.321039091172274</v>
+        <v>170.83254188661647</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10848,16 +10848,16 @@
         <v>286</v>
       </c>
       <c r="Y27" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Z27" t="s">
         <v>320</v>
       </c>
       <c r="AA27">
-        <v>0.99853082183379016</v>
+        <v>0.99897010067703429</v>
       </c>
       <c r="AB27">
-        <v>26.934933047180987</v>
+        <v>18.881487587705607</v>
       </c>
       <c r="AD27" t="s">
         <v>251</v>
@@ -10890,10 +10890,10 @@
         <v>395</v>
       </c>
       <c r="AO27">
-        <v>0.99907918970282927</v>
+        <v>0.99844423111858249</v>
       </c>
       <c r="AP27">
-        <v>16.881522114796713</v>
+        <v>28.522429492654361</v>
       </c>
       <c r="AR27" t="s">
         <v>251</v>
@@ -10920,16 +10920,16 @@
         <v>428</v>
       </c>
       <c r="BA27" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="BB27" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="BC27">
-        <v>0.98627052110774238</v>
+        <v>0.99560758626248369</v>
       </c>
       <c r="BD27">
-        <v>251.70711302472259</v>
+        <v>80.527585187798735</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10994,16 +10994,16 @@
         <v>288</v>
       </c>
       <c r="Y28" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Z28" t="s">
         <v>321</v>
       </c>
       <c r="AA28">
-        <v>0.99886029773300145</v>
+        <v>0.99841532396070098</v>
       </c>
       <c r="AB28">
-        <v>20.894541561640985</v>
+        <v>29.052394053816059</v>
       </c>
       <c r="AR28" t="s">
         <v>251</v>
@@ -11030,16 +11030,16 @@
         <v>430</v>
       </c>
       <c r="BA28" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="BB28" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="BC28">
-        <v>0.99278784076394344</v>
+        <v>0.99160116355990502</v>
       </c>
       <c r="BD28">
-        <v>132.22291932770449</v>
+        <v>153.97866806840764</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11104,16 +11104,16 @@
         <v>290</v>
       </c>
       <c r="Y29" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="Z29" t="s">
         <v>322</v>
       </c>
       <c r="AA29">
-        <v>0.99544314722299798</v>
+        <v>0.99748798960410945</v>
       </c>
       <c r="AB29">
-        <v>83.542300911704686</v>
+        <v>46.05352392465965</v>
       </c>
       <c r="AR29" t="s">
         <v>251</v>
@@ -11140,16 +11140,16 @@
         <v>432</v>
       </c>
       <c r="BA29" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="BB29" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="BC29">
-        <v>0.98009770506351668</v>
+        <v>0.99255179421932938</v>
       </c>
       <c r="BD29">
-        <v>364.87540716886002</v>
+        <v>136.55043931229389</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11214,16 +11214,16 @@
         <v>292</v>
       </c>
       <c r="Y30" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Z30" t="s">
         <v>323</v>
       </c>
       <c r="AA30">
-        <v>0.99881634769332572</v>
+        <v>0.99853082183379016</v>
       </c>
       <c r="AB30">
-        <v>21.700292289029083</v>
+        <v>26.934933047180987</v>
       </c>
       <c r="AR30" t="s">
         <v>251</v>
@@ -11250,16 +11250,16 @@
         <v>434</v>
       </c>
       <c r="BA30" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="BB30" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="BC30">
-        <v>0.9969294297150163</v>
+        <v>0.98877515176124608</v>
       </c>
       <c r="BD30">
-        <v>56.2937885580344</v>
+        <v>205.78888437715531</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11324,16 +11324,16 @@
         <v>294</v>
       </c>
       <c r="Y31" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="Z31" t="s">
         <v>324</v>
       </c>
       <c r="AA31">
-        <v>0.99902825268538287</v>
+        <v>0.99886029773300145</v>
       </c>
       <c r="AB31">
-        <v>17.815367434646582</v>
+        <v>20.894541561640985</v>
       </c>
       <c r="AR31" t="s">
         <v>251</v>
@@ -11360,16 +11360,16 @@
         <v>436</v>
       </c>
       <c r="BA31" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="BB31" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="BC31">
-        <v>0.99534342454901092</v>
+        <v>0.98791946624258509</v>
       </c>
       <c r="BD31">
-        <v>85.370549934800536</v>
+        <v>221.4764522192738</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11434,16 +11434,16 @@
         <v>296</v>
       </c>
       <c r="Y32" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Z32" t="s">
         <v>325</v>
       </c>
       <c r="AA32">
-        <v>0.99790242535065354</v>
+        <v>0.99916935310675503</v>
       </c>
       <c r="AB32">
-        <v>38.455535238019358</v>
+        <v>15.22852637615807</v>
       </c>
       <c r="AR32" t="s">
         <v>251</v>
@@ -11476,10 +11476,10 @@
         <v>482</v>
       </c>
       <c r="BC32">
-        <v>0.98877515176124608</v>
+        <v>0.99509603189170837</v>
       </c>
       <c r="BD32">
-        <v>205.78888437715531</v>
+        <v>89.90608198534612</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -11544,16 +11544,16 @@
         <v>298</v>
       </c>
       <c r="Y33" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z33" t="s">
         <v>326</v>
       </c>
       <c r="AA33">
-        <v>0.99922833574773007</v>
+        <v>0.99838245441178075</v>
       </c>
       <c r="AB33">
-        <v>14.14717795828226</v>
+        <v>29.65500245068538</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -11618,16 +11618,16 @@
         <v>300</v>
       </c>
       <c r="Y34" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="Z34" t="s">
         <v>327</v>
       </c>
       <c r="AA34">
-        <v>0.99897010067703429</v>
+        <v>0.99544314722299798</v>
       </c>
       <c r="AB34">
-        <v>18.881487587705607</v>
+        <v>83.542300911704686</v>
       </c>
     </row>
   </sheetData>
@@ -11636,7 +11636,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF1DE042-6775-4F8E-B326-CEFF0CAF2898}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AAEEC44-F5B6-40A0-985F-CD074F19F2E3}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11748,7 +11748,7 @@
         <v>483</v>
       </c>
       <c r="K11" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="L11">
         <v>9.9561879268440521</v>
@@ -11781,7 +11781,7 @@
         <v>517</v>
       </c>
       <c r="X11" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="Y11">
         <v>5.7030000000000003</v>
@@ -11816,7 +11816,7 @@
         <v>485</v>
       </c>
       <c r="K12" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="L12">
         <v>15.610469208056319</v>
@@ -11849,7 +11849,7 @@
         <v>519</v>
       </c>
       <c r="X12" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="Y12">
         <v>3.2370000000000001</v>
@@ -11884,7 +11884,7 @@
         <v>487</v>
       </c>
       <c r="K13" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="L13">
         <v>38.93604588989777</v>
@@ -11917,7 +11917,7 @@
         <v>521</v>
       </c>
       <c r="X13" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="Y13">
         <v>0.73950000000000005</v>
@@ -11952,7 +11952,7 @@
         <v>489</v>
       </c>
       <c r="K14" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="L14">
         <v>3.4061833906252343</v>
@@ -11985,7 +11985,7 @@
         <v>523</v>
       </c>
       <c r="X14" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="Y14">
         <v>17.418749999999999</v>
@@ -12020,7 +12020,7 @@
         <v>491</v>
       </c>
       <c r="K15" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L15">
         <v>10.05531955531686</v>
@@ -12053,7 +12053,7 @@
         <v>525</v>
       </c>
       <c r="X15" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="Y15">
         <v>75.501750000000001</v>
@@ -12088,7 +12088,7 @@
         <v>493</v>
       </c>
       <c r="K16" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L16">
         <v>11.000319473014851</v>
@@ -12121,7 +12121,7 @@
         <v>527</v>
       </c>
       <c r="X16" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="Y16">
         <v>26.099250000000001</v>
@@ -12156,7 +12156,7 @@
         <v>495</v>
       </c>
       <c r="K17" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="L17">
         <v>1.9758785540112649</v>
@@ -12189,7 +12189,7 @@
         <v>529</v>
       </c>
       <c r="X17" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="Y17">
         <v>6.7657499999999997</v>
@@ -12224,7 +12224,7 @@
         <v>497</v>
       </c>
       <c r="K18" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="L18">
         <v>10.302711276720984</v>
@@ -12257,7 +12257,7 @@
         <v>531</v>
       </c>
       <c r="X18" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="Y18">
         <v>18.204750000000001</v>
@@ -12292,7 +12292,7 @@
         <v>499</v>
       </c>
       <c r="K19" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="L19">
         <v>21.084725957939643</v>
@@ -12325,7 +12325,7 @@
         <v>533</v>
       </c>
       <c r="X19" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="Y19">
         <v>53.964750000000002</v>
@@ -12360,7 +12360,7 @@
         <v>501</v>
       </c>
       <c r="K20" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="L20">
         <v>7.8234985450080243</v>
@@ -12393,7 +12393,7 @@
         <v>535</v>
       </c>
       <c r="X20" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="Y20">
         <v>32.474249999999998</v>
@@ -12428,7 +12428,7 @@
         <v>503</v>
       </c>
       <c r="K21" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="L21">
         <v>35.48135454794123</v>
@@ -12461,7 +12461,7 @@
         <v>537</v>
       </c>
       <c r="X21" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Y21">
         <v>24.771750000000001</v>
@@ -12496,7 +12496,7 @@
         <v>505</v>
       </c>
       <c r="K22" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L22">
         <v>31.11916467188631</v>
@@ -12529,7 +12529,7 @@
         <v>539</v>
       </c>
       <c r="X22" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="Y22">
         <v>34.518000000000001</v>
@@ -12564,7 +12564,7 @@
         <v>507</v>
       </c>
       <c r="K23" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="L23">
         <v>4.5001608244833662</v>
@@ -12597,7 +12597,7 @@
         <v>541</v>
       </c>
       <c r="X23" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="Y23">
         <v>13.3995</v>
@@ -12632,7 +12632,7 @@
         <v>509</v>
       </c>
       <c r="K24" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="L24">
         <v>9.5500952124569967</v>
@@ -12665,7 +12665,7 @@
         <v>543</v>
       </c>
       <c r="X24" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="Y24">
         <v>38.413499999999999</v>
@@ -12700,7 +12700,7 @@
         <v>511</v>
       </c>
       <c r="K25" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="L25">
         <v>5.3426370365388722</v>
@@ -12733,7 +12733,7 @@
         <v>545</v>
       </c>
       <c r="X25" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="Y25">
         <v>15.254250000000001</v>
@@ -12768,7 +12768,7 @@
         <v>513</v>
       </c>
       <c r="K26" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="L26">
         <v>1.0928295776667281</v>
@@ -12801,7 +12801,7 @@
         <v>547</v>
       </c>
       <c r="X26" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="Y26">
         <v>16.820250000000001</v>
@@ -12836,7 +12836,7 @@
         <v>515</v>
       </c>
       <c r="K27" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="L27">
         <v>0.94607061901700107</v>
@@ -12869,7 +12869,7 @@
         <v>549</v>
       </c>
       <c r="X27" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="Y27">
         <v>32.364750000000001</v>
@@ -12904,7 +12904,7 @@
         <v>551</v>
       </c>
       <c r="X28" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="Y28">
         <v>20.224499999999999</v>
@@ -12939,7 +12939,7 @@
         <v>553</v>
       </c>
       <c r="X29" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="Y29">
         <v>13.347</v>
@@ -12974,7 +12974,7 @@
         <v>555</v>
       </c>
       <c r="X30" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="Y30">
         <v>3.7177500000000001</v>
@@ -13009,7 +13009,7 @@
         <v>557</v>
       </c>
       <c r="X31" t="s">
-        <v>469</v>
+        <v>440</v>
       </c>
       <c r="Y31">
         <v>9.6434999999999995</v>
@@ -13044,7 +13044,7 @@
         <v>559</v>
       </c>
       <c r="X32" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="Y32">
         <v>38.509500000000003</v>
@@ -13059,7 +13059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A446C2B2-69C0-4009-839A-49E6E5C38F02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF88341-4207-419A-9E26-25DFD0B7A225}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14876,7 +14876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{310A0249-DEE6-46E8-BA77-B1DC9B60472F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{641C8B5C-4984-4A97-AA46-6DA10F64942E}">
   <dimension ref="B2:M187"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_VNM_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_VNM_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD3215D0-7BC3-4C45-BDF4-FF56966E7B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA478FD-A360-4AA9-B115-1133DDC510DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3657" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3657" uniqueCount="1139">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -3543,6 +3543,9 @@
   <si>
     <t>Transformer: e_w881704523-220 → e_w881704523-500</t>
   </si>
+  <si>
+    <t>e_VN1003-500,e_VN1005-500,e_VN1008-500,e_VN1010-500,e_VN1014-500,e_VN1016-500,e_VN1019-500,e_VN1020-500,e_VN1022-500,e_VN1024-220,e_VN1130-500,e_VN1133-220,e_VN1134-220,e_VN1137-500,e_VN1138-220,e_VN1139-220,e_VN1140-500,e_VN1141-220,e_VN1141-500,e_VN1142-500,e_VN1145-220,e_VN1146-500,e_VN1147-220,e_VN1149-500,e_VN1153-220,e_VN1154-220,e_VN1157-220,e_VN1178-500,e_VN1179-220,e_VN1184-500,e_VN1187-500,e_VN1188-220,e_VN1191-500,e_VN1192-500,e_VN1196-500,e_VN1198-500,e_VN1206-220,e_VN1208-500,e_VN1209-500,e_VN1210-500,e_VN1213-220,e_VN1218-220,e_VN1219-220,e_VN1223-220,e_VN1223-500,e_VN1224-500,e_VN1226-500,e_VN1228-220,e_VN181-500,e_VN183-500,e_VN186-500,e_VN188-500,e_VN189-500,e_VN192-500,e_VN195-220,e_VN195-500,e_VN196-500,e_VN197-500,e_VN198-500,e_VN199-500,e_VN2-220,e_VN200-500,e_VN201-500,e_VN202-500,e_VN203-220,e_VN203-500,e_VN205-500,e_VN206-500,e_VN207-500,e_VN209-220,e_VN210-500,e_VN211-500,e_VN212-500,e_VN213-500,e_VN214-500,e_VN215-500,e_VN216-500,e_VN217-500,e_VN218-500,e_VN224-500,e_VN225-500,e_VN226-500,e_VN229-500,e_VN230-220,e_VN230-500,e_VN232-220,e_VN251-220,e_VN252-220,e_VN274-220,e_VN310-220,e_VN323-500,e_VN328-500,e_VN334-500,e_VN365-220,e_VN383-220,e_VN391-500,e_VN392-500,e_VN393-500,e_VN394-500,e_VN395-500,e_VN396-500,e_VN397-500,e_VN398-500,e_VN400-500,e_VN401-500,e_VN402-500,e_VN404-500,e_VN405-500,e_VN406-500,e_VN408-220,e_VN408-500,e_VN409-500,e_VN410-220,e_VN411-500,e_VN412-500,e_VN413-220,e_VN414-500,e_VN418-500,e_VN419-500,e_VN421-500,e_VN422-500,e_VN427-500,e_VN428-500,e_VN429-500,e_VN430-500,e_VN431-500,e_VN432-500,e_VN433-500,e_VN434-500,e_VN435-500,e_VN436-500,e_VN437-500,e_VN438-500,e_VN439-500,e_VN440-500,e_VN441-500,e_VN442-500,e_VN449-500,e_VN451-220,e_VN452-500,e_VN454-500,e_VN455-500,e_VN509-500,e_VN511-220,e_VN511-500,e_VN512-500,e_VN513-500,e_VN514-500,e_VN515-500,e_VN516-500,e_VN517-500,e_VN518-500,e_VN519-220,e_VN519-500,e_VN520-500,e_VN521-220,e_VN521-500,e_VN522-500,e_VN523-500,e_VN524-500,e_VN525-500,e_VN526-500,e_VN527-500,e_VN528-500,e_VN529-500,e_VN533-220,e_VN534-220,e_VN534-500,e_VN536-220,e_VN537-220,e_VN538-220,e_VN539-220,e_VN540-220,e_VN589-500,e_VN592-500,e_VN595-500,e_VN597-500,e_VN598-500,e_VN624-220,e_VN801-500,e_VN802-500,e_VN803-500,e_VN805-500,e_VN806-500,e_VN807-500,e_VN813-500,e_VN814-500,e_VN815-500,e_VN819-500,e_VN823-500,e_VN824-500,e_VN825-500,e_VN826-500,e_VN836-220,e_VN837-220,e_VN902-220,e_VN937-220,e_VN988-220,e_VN994-500,e_VN998-500,e_VN999-500,e_w1018528434-220,e_w1044469623-220,e_w1045125739-220,e_w1047280375-220,e_w1047400696-220,e_w1047400696-500,e_w1052065872-220,e_w1052125064-220,e_w1087113517-220,e_w1091686589-220,e_w1091782693-220,e_w1176845159-220,e_w1176845164-220,e_w1183902227-500,e_w1216970886-220,e_w1216970886-500,e_w1245195233-220,e_w1258175914-220,e_w1265274413-220,e_w1265274426-500,e_w1265612937-220,e_w1272088369-220,e_w1273255946-220,e_w1273527149-220,e_w1273527210-220,e_w1273948701-220,e_w1274076450-220,e_w1274076450-500,e_w1274466549-220,e_w1320784083-220,e_w1320784083-500,e_w1374565925-220,e_w1376430795-220,e_w1376430795-500,e_w241065371-220,e_w306295536-220,e_w306295536-500,e_w306295540-220,e_w307638314-220,e_w315766007-220,e_w315766015-220,e_w400645442-220,e_w400791086-220,e_w400791086-500,e_w401042494-220,e_w401532710-220,e_w468821783-220,e_w468821783-500,e_w548717060-220,e_w548717060-500,e_w548723124-220,e_w548752026-220,e_w548869165-220,e_w548869165-230,e_w548970118-220,e_w549038673-220,e_w549296358-220,e_w549380074-220,e_w549400050-220,e_w549400050-500,e_w549400051-220,e_w549577079-220,e_w549914200-220,e_w549941525-220,e_w549959350-220,e_w549959354-220,e_w630750798-220,e_w630750798-500,e_w715041211-220,e_w744217936-220,e_w762471641-220,e_w827889590-500,e_w827889600-220,e_w827889600-500,e_w967849373-220</t>
+  </si>
 </sst>
 </file>
 
@@ -3556,7 +3559,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3704,15 +3707,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3804,11 +3800,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -4023,7 +4014,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4043,9 +4034,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -4437,7 +4427,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4457,9 +4446,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="20">
+  <cellStyles count="19">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
-    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -5435,7 +5423,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_VN1003-500,e_VN1005-500,e_VN1008-500,e_VN1010-500,e_VN1014-500,e_VN1016-500,e_VN1019-500,e_VN1020-500,e_VN1022-500,e_VN1024-220,e_VN1130-500,e_VN1133-220,e_VN1134-220,e_VN1137-500,e_VN1138-220,e_VN1139-220,e_VN1140-500,e_VN1141-220,e_VN1141-500,e_VN1142-500,e_VN1145-220,e_VN1146-500,e_VN1147-220,e_VN1149-500,e_VN1153-220,e_VN1154-220,e_VN1157-220,e_VN1178-500,e_VN1179-220,e_VN1184-500,e_VN1187-500,e_VN1188-220,e_VN1191-500,e_VN1192-500,e_VN1196-500,e_VN1198-500,e_VN1206-220,e_VN1208-500,e_VN1209-500,e_VN1210-500,e_VN1213-220,e_VN1218-220,e_VN1219-220,e_VN1223-220,e_VN1223-500,e_VN1224-500,e_VN1226-500,e_VN1228-220,e_VN181-500,e_VN183-500,e_VN186-500,e_VN188-500,e_VN189-500,e_VN192-500,e_VN195-220,e_VN195-500,e_VN196-500,e_VN197-500,e_VN198-500,e_VN199-500,e_VN2-220,e_VN200-500,e_VN201-500,e_VN202-500,e_VN203-220,e_VN203-500,e_VN205-500,e_VN206-500,e_VN207-500,e_VN209-220,e_VN210-500,e_VN211-500,e_VN212-500,e_VN213-500,e_VN214-500,e_VN215-500,e_VN216-500,e_VN217-500,e_VN218-500,e_VN224-500,e_VN225-500,e_VN226-500,e_VN229-500,e_VN230-220,e_VN230-500,e_VN232-220,e_VN251-220,e_VN252-220,e_VN274-220,e_VN310-220,e_VN323-500,e_VN328-500,e_VN334-500,e_VN365-220,e_VN383-220,e_VN391-500,e_VN392-500,e_VN393-500,e_VN394-500,e_VN395-500,e_VN396-500,e_VN397-500,e_VN398-500,e_VN400-500,e_VN401-500,e_VN402-500,e_VN404-500,e_VN405-500,e_VN406-500,e_VN408-220,e_VN408-500,e_VN409-500,e_VN410-220,e_VN411-500,e_VN412-500,e_VN413-220,e_VN414-500,e_VN418-500,e_VN419-500,e_VN421-500,e_VN422-500,e_VN427-500,e_VN428-500,e_VN429-500,e_VN430-500,e_VN431-500,e_VN432-500,e_VN433-500,e_VN434-500,e_VN435-500,e_VN436-500,e_VN437-500,e_VN438-500,e_VN439-500,e_VN440-500,e_VN441-500,e_VN442-500,e_VN449-500,e_VN451-220,e_VN452-500,e_VN454-500,e_VN455-500,e_VN509-500,e_VN511-220,e_VN511-500,e_VN512-500,e_VN513-500,e_VN514-500,e_VN515-500,e_VN516-500,e_VN517-500,e_VN518-500,e_VN519-220,e_VN519-500,e_VN520-500,e_VN521-220,e_VN521-500,e_VN522-500,e_VN523-500,e_VN524-500,e_VN525-500,e_VN526-500,e_VN527-500,e_VN528-500,e_VN529-500,e_VN533-220,e_VN534-220,e_VN534-500,e_VN536-220,e_VN537-220,e_VN538-220,e_VN539-220,e_VN540-220,e_VN589-500,e_VN592-500,e_VN595-500,e_VN597-500,e_VN598-500,e_VN624-220,e_VN801-500,e_VN802-500,e_VN803-500,e_VN805-500,e_VN806-500,e_VN807-500,e_VN813-500,e_VN814-500,e_VN815-500,e_VN819-500,e_VN823-500,e_VN824-500,e_VN825-500,e_VN826-500,e_VN836-220,e_VN837-220,e_VN902-220,e_VN937-220,e_VN988-220,e_VN994-500,e_VN998-500,e_VN999-500,e_w1018528434-220,e_w1044469623-220,e_w1045125739-220,e_w1047280375-220,e_w1047400696-220,e_w1047400696-500,e_w1052065872-220,e_w1052125064-220,e_w1087113517-220,e_w1091686589-220,e_w1091782693-220,e_w1176845159-220,e_w1176845164-220,e_w1183902227-500,e_w1216970886-220,e_w1216970886-500,e_w1245195233-220,e_w1258175914-220,e_w1265274413-220,e_w1265274426-500,e_w1265612937-220,e_w1272088369-220,e_w1273255946-220,e_w1273527149-220,e_w1273527210-220,e_w1273948701-220,e_w1274076450-220,e_w1274076450-500,e_w1274466549-220,e_w1320784083-220,e_w1320784083-500,e_w1374565925-220,e_w1376430795-220,e_w1376430795-500,e_w241065371-220,e_w306295536-220,e_w306295536-500,e_w306295540-220,e_w307638314-220,e_w315766007-220,e_w315766015-220,e_w400645442-220,e_w400791086-220,e_w400791086-500,e_w401042494-220,e_w401532710-220,e_w468821783-220,e_w468821783-500,e_w548717060-220,e_w548717060-500,e_w548723124-220,e_w548752026-220,e_w548869165-220,e_w548869165-230,e_w548970118-220,e_w549038673-220,e_w549296358-220,e_w549380074-220,e_w549400050-220,e_w549400050-500,e_w549400051-220,e_w549577079-220,e_w549914200-220,e_w549941525-220,e_w549959350-220,e_w549959354-220,e_w630750798-220,e_w630750798-500,e_w715041211-220,e_w744217936-220,e_w762471641-220,e_w827889590-500,e_w827889600-220,e_w827889600-500,e_w967849373-220</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5457,7 +5445,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_VN1003-500,e_VN1005-500,e_VN1008-500,e_VN1010-500,e_VN1014-500,e_VN1016-500,e_VN1019-500,e_VN1020-500,e_VN1022-500,e_VN1024-220,e_VN1130-500,e_VN1133-220,e_VN1134-220,e_VN1137-500,e_VN1138-220,e_VN1139-220,e_VN1140-500,e_VN1141-220,e_VN1141-500,e_VN1142-500,e_VN1145-220,e_VN1146-500,e_VN1147-220,e_VN1149-500,e_VN1153-220,e_VN1154-220,e_VN1157-220,e_VN1178-500,e_VN1179-220,e_VN1184-500,e_VN1187-500,e_VN1188-220,e_VN1191-500,e_VN1192-500,e_VN1196-500,e_VN1198-500,e_VN1206-220,e_VN1208-500,e_VN1209-500,e_VN1210-500,e_VN1213-220,e_VN1218-220,e_VN1219-220,e_VN1223-220,e_VN1223-500,e_VN1224-500,e_VN1226-500,e_VN1228-220,e_VN181-500,e_VN183-500,e_VN186-500,e_VN188-500,e_VN189-500,e_VN192-500,e_VN195-220,e_VN195-500,e_VN196-500,e_VN197-500,e_VN198-500,e_VN199-500,e_VN2-220,e_VN200-500,e_VN201-500,e_VN202-500,e_VN203-220,e_VN203-500,e_VN205-500,e_VN206-500,e_VN207-500,e_VN209-220,e_VN210-500,e_VN211-500,e_VN212-500,e_VN213-500,e_VN214-500,e_VN215-500,e_VN216-500,e_VN217-500,e_VN218-500,e_VN224-500,e_VN225-500,e_VN226-500,e_VN229-500,e_VN230-220,e_VN230-500,e_VN232-220,e_VN251-220,e_VN252-220,e_VN274-220,e_VN310-220,e_VN323-500,e_VN328-500,e_VN334-500,e_VN365-220,e_VN383-220,e_VN391-500,e_VN392-500,e_VN393-500,e_VN394-500,e_VN395-500,e_VN396-500,e_VN397-500,e_VN398-500,e_VN400-500,e_VN401-500,e_VN402-500,e_VN404-500,e_VN405-500,e_VN406-500,e_VN408-220,e_VN408-500,e_VN409-500,e_VN410-220,e_VN411-500,e_VN412-500,e_VN413-220,e_VN414-500,e_VN418-500,e_VN419-500,e_VN421-500,e_VN422-500,e_VN427-500,e_VN428-500,e_VN429-500,e_VN430-500,e_VN431-500,e_VN432-500,e_VN433-500,e_VN434-500,e_VN435-500,e_VN436-500,e_VN437-500,e_VN438-500,e_VN439-500,e_VN440-500,e_VN441-500,e_VN442-500,e_VN449-500,e_VN451-220,e_VN452-500,e_VN454-500,e_VN455-500,e_VN509-500,e_VN511-220,e_VN511-500,e_VN512-500,e_VN513-500,e_VN514-500,e_VN515-500,e_VN516-500,e_VN517-500,e_VN518-500,e_VN519-220,e_VN519-500,e_VN520-500,e_VN521-220,e_VN521-500,e_VN522-500,e_VN523-500,e_VN524-500,e_VN525-500,e_VN526-500,e_VN527-500,e_VN528-500,e_VN529-500,e_VN533-220,e_VN534-220,e_VN534-500,e_VN536-220,e_VN537-220,e_VN538-220,e_VN539-220,e_VN540-220,e_VN589-500,e_VN592-500,e_VN595-500,e_VN597-500,e_VN598-500,e_VN624-220,e_VN801-500,e_VN802-500,e_VN803-500,e_VN805-500,e_VN806-500,e_VN807-500,e_VN813-500,e_VN814-500,e_VN815-500,e_VN819-500,e_VN823-500,e_VN824-500,e_VN825-500,e_VN826-500,e_VN836-220,e_VN837-220,e_VN902-220,e_VN937-220,e_VN988-220,e_VN994-500,e_VN998-500,e_VN999-500,e_w1018528434-220,e_w1044469623-220,e_w1045125739-220,e_w1047280375-220,e_w1047400696-220,e_w1047400696-500,e_w1052065872-220,e_w1052125064-220,e_w1087113517-220,e_w1091686589-220,e_w1091782693-220,e_w1176845159-220,e_w1176845164-220,e_w1183902227-500,e_w1216970886-220,e_w1216970886-500,e_w1245195233-220,e_w1258175914-220,e_w1265274413-220,e_w1265274426-500,e_w1265612937-220,e_w1272088369-220,e_w1273255946-220,e_w1273527149-220,e_w1273527210-220,e_w1273948701-220,e_w1274076450-220,e_w1274076450-500,e_w1274466549-220,e_w1320784083-220,e_w1320784083-500,e_w1374565925-220,e_w1376430795-220,e_w1376430795-500,e_w241065371-220,e_w306295536-220,e_w306295536-500,e_w306295540-220,e_w307638314-220,e_w315766007-220,e_w315766015-220,e_w400645442-220,e_w400791086-220,e_w400791086-500,e_w401042494-220,e_w401532710-220,e_w468821783-220,e_w468821783-500,e_w548717060-220,e_w548717060-500,e_w548723124-220,e_w548752026-220,e_w548869165-220,e_w548869165-230,e_w548970118-220,e_w549038673-220,e_w549296358-220,e_w549380074-220,e_w549400050-220,e_w549400050-500,e_w549400051-220,e_w549577079-220,e_w549914200-220,e_w549941525-220,e_w549959350-220,e_w549959354-220,e_w630750798-220,e_w630750798-500,e_w715041211-220,e_w744217936-220,e_w762471641-220,e_w827889590-500,e_w827889600-220,e_w827889600-500,e_w967849373-220</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5471,8 +5459,8 @@
       <c r="S28">
         <v>50</v>
       </c>
-      <c r="V28" s="147" t="s">
-        <v>19</v>
+      <c r="V28" t="s">
+        <v>1138</v>
       </c>
     </row>
   </sheetData>
@@ -7018,25 +7006,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="147" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="148"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="148" t="s">
+      <c r="G1" s="147"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="147" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="151" t="s">
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="150" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -7082,7 +7070,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="152"/>
+      <c r="O2" s="151"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -7127,7 +7115,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="152"/>
+      <c r="O3" s="151"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -7169,7 +7157,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="153"/>
+      <c r="O4" s="152"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>

--- a/VerveStacks_VNM_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_VNM_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC7A6A5E-7E0C-42D1-A2CD-6E13444326F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DDB00D5-8D3C-4F91-9C2F-E9243422ED26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -919,6 +919,18 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_007</t>
   </si>
   <si>
@@ -943,6 +955,72 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_012</t>
   </si>
   <si>
@@ -961,84 +1039,6 @@
     <t>connecting solar to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1057,6 +1057,12 @@
     <t>e_VN1152-220,e_w548752026-220,e_VN1099-500,e_w1273948690-220,e_w1273948701-220,e_w1273898576-220,e_w400474243-220,e_VN988-220,e_w1273527149-220</t>
   </si>
   <si>
+    <t>e_w1264568817-220,e_w1264568832-220,e_VN132-220,e_w483057097-220,e_VN12-220,e_VN118-500,e_w1240467340-220</t>
+  </si>
+  <si>
+    <t>e_VN477-500,e_VN464-500,e_VN484-500,e_VN476-500,e_VN467-500,e_VN569-220,e_VN510-220,e_VN488-220,e_VN471-500</t>
+  </si>
+  <si>
     <t>e_VN1206-220,e_VN1186-220,e_w548970103-220,e_w548970109-220,e_VN1188-220,e_w967849373-220,e_VN1227-220,e_w548970118-220,e_w548869165-230,e_w548869165-220,e_w773079147-220,e_VN1164-500</t>
   </si>
   <si>
@@ -1069,6 +1075,39 @@
     <t>e_VN770-500,e_VN748-500,e_VN844-500,e_VN753-220,e_VN714-220,e_VN836-220,e_w1273255944-220,e_w549197475-220,e_w549296358-220</t>
   </si>
   <si>
+    <t>e_w548970103-220,e_w548970101-220,e_VN1227-220,e_VN1207-500,e_w549005377-220,e_VN1210-500,e_w827889600-220,e_w1052065872-220,e_w744217936-220</t>
+  </si>
+  <si>
+    <t>e_VN900-500,e_VN855-500,e_w1273328710-220,e_VN1013-220,e_VN907-220,e_VN832-500,e_w400413521-220,e_w400482074-220,e_VN920-500,e_VN816-500</t>
+  </si>
+  <si>
+    <t>e_VN8-500,e_w893223532-220,e_VN16-500,e_VN15-500,e_w1263573984-220,e_VN2-220</t>
+  </si>
+  <si>
+    <t>e_VN367-500,e_VN384-500,e_VN374-500,e_VN447-500,e_VN433-500</t>
+  </si>
+  <si>
+    <t>e_w1050835279-220,e_VN351-220</t>
+  </si>
+  <si>
+    <t>e_w1050835279-220,e_VN278-500,e_VN235-500,e_VN321-220,e_w857794232-220,e_VN280-500</t>
+  </si>
+  <si>
+    <t>e_w439941742-220,e_VN556-500,e_VN512-500,e_w401042494-220,e_w1233471417-220,e_VN585-500,e_VN537-220,e_VN522-500,e_w1258175914-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>e_VN1130-500,e_w1051605925-220,e_w775832889-220,e_VN1156-500,e_w1052403240-220,e_VN983-220,e_w1176845159-220,e_VN1154-220,e_VN1097-220,e_VN987-500,e_VN930-500,e_VN918-500,e_w1212041269-220,e_VN1017-500</t>
+  </si>
+  <si>
+    <t>e_VN321-220,e_w1267181647-220,e_VN297-500,e_VN128-500,e_VN324-500,e_VN322-220,e_VN314-500,e_VN256-220,e_w1320784083-500,e_VN320-220,e_VN312-220,e_w1036283936-220,e_w750907640-220</t>
+  </si>
+  <si>
+    <t>e_VN3-220,e_w1240393348-220</t>
+  </si>
+  <si>
+    <t>e_VN738-500,e_w549380074-220,e_w401532710-220,e_VN624-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN644-500</t>
+  </si>
+  <si>
     <t>e_VN310-220,e_w1045125739-220,e_VN152-500,e_w469414362-220,e_w241065371-220,e_VN167-220,e_w827889590-500,e_w1245195233-220</t>
   </si>
   <si>
@@ -1078,43 +1117,88 @@
     <t>e_VN390-500,e_VN375-220,e_VN457-500,e_VN441-500,e_w630750798-500</t>
   </si>
   <si>
-    <t>e_w548970103-220,e_w548970101-220,e_VN1227-220,e_VN1207-500,e_w549005377-220,e_VN1210-500,e_w827889600-220,e_w1052065872-220,e_w744217936-220</t>
-  </si>
-  <si>
-    <t>e_VN900-500,e_VN855-500,e_w1273328710-220,e_VN1013-220,e_VN907-220,e_VN832-500,e_w400413521-220,e_w400482074-220,e_VN920-500,e_VN816-500</t>
-  </si>
-  <si>
-    <t>e_w1050835279-220,e_VN278-500,e_VN235-500,e_VN321-220,e_w857794232-220,e_VN280-500</t>
-  </si>
-  <si>
-    <t>e_w439941742-220,e_VN556-500,e_VN512-500,e_w401042494-220,e_w1233471417-220,e_VN585-500,e_VN537-220,e_VN522-500,e_w1258175914-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>e_VN321-220,e_w1267181647-220,e_VN297-500,e_VN128-500,e_VN324-500,e_VN322-220,e_VN314-500,e_VN256-220,e_w1320784083-500,e_VN320-220,e_VN312-220,e_w1036283936-220,e_w750907640-220</t>
-  </si>
-  <si>
-    <t>e_VN3-220,e_w1240393348-220</t>
-  </si>
-  <si>
-    <t>e_VN738-500,e_w549380074-220,e_w401532710-220,e_VN624-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN644-500</t>
-  </si>
-  <si>
-    <t>e_w1050835279-220,e_VN351-220</t>
-  </si>
-  <si>
-    <t>e_VN8-500,e_w893223532-220,e_VN16-500,e_VN15-500,e_w1263573984-220,e_VN2-220</t>
-  </si>
-  <si>
-    <t>e_VN367-500,e_VN384-500,e_VN374-500,e_VN447-500,e_VN433-500</t>
-  </si>
-  <si>
-    <t>e_w1264568817-220,e_w1264568832-220,e_VN132-220,e_w483057097-220,e_VN12-220,e_VN118-500,e_w1240467340-220</t>
-  </si>
-  <si>
-    <t>e_VN477-500,e_VN464-500,e_VN484-500,e_VN476-500,e_VN467-500,e_VN569-220,e_VN510-220,e_VN488-220,e_VN471-500</t>
-  </si>
-  <si>
-    <t>e_VN1130-500,e_w1051605925-220,e_w775832889-220,e_VN1156-500,e_w1052403240-220,e_VN983-220,e_w1176845159-220,e_VN1154-220,e_VN1097-220,e_VN987-500,e_VN930-500,e_VN918-500,e_w1212041269-220,e_VN1017-500</t>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wonelc_won_001</t>
@@ -1123,16 +1207,10 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wonelc_won_006</t>
@@ -1141,82 +1219,88 @@
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_VN384-500,e_VN447-500,e_VN433-500,e_VN477-500,e_VN464-500,e_VN457-500,e_VN484-500,e_VN476-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_VN1156-500,e_VN1154-220,e_VN1152-220</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_VN488-220,e_VN471-500,e_VN512-500,e_w401042494-220</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w775832889-220,e_VN918-500,e_VN900-500,e_VN855-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w1036283936-220,e_VN118-500,e_w483057097-220,e_VN152-500,e_w469414362-220,e_VN3-220,e_VN167-220,e_w1240393348-220,e_w827889590-500,e_w1245195233-220</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_VN648-500,e_VN753-220,e_VN714-220,e_VN702-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_VN345-220,e_VN324-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w1273328710-220,e_VN738-500,e_w549380074-220,e_VN832-500,e_w400413521-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN770-500,e_VN748-500,e_VN728-220,e_VN695-220,e_w1273898576-220,e_w400474243-220,e_VN988-220,e_w1273527149-220</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_VN1206-220,e_VN1186-220,e_w548970109-220,e_VN1188-220</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w1240393348-220</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_VN623-500,e_w1258175914-220,e_w1272088369-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_VN1206-220,e_w548970103-220,e_VN1227-220,e_w548970118-220,e_VN1207-500,e_VN1210-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_VN537-220,e_VN522-500,e_w549400051-220,e_VN575-220</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_VN374-500,e_VN390-500,e_VN375-220,e_VN441-500,e_w630750798-500,e_VN467-500</t>
   </si>
   <si>
     <t>elc_won_001</t>
@@ -1225,16 +1309,10 @@
     <t>e_w1320784083-500,e_VN320-220,e_VN312-220,e_w750907640-220,e_VN310-220,e_w1045125739-220,e_w241065371-220,e_w715041211-220,e_w1245195233-220</t>
   </si>
   <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w775832889-220,e_VN918-500,e_VN900-500,e_VN855-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_VN1156-500,e_VN1154-220,e_VN1152-220</t>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w548970103-220,e_w548970101-220,e_w549005377-220,e_w827889600-220,e_w1052065872-220,e_w744217936-220,e_w548752026-220,e_VN1099-500,e_w1273948690-220,e_w400482074-220,e_w1273948701-220</t>
   </si>
   <si>
     <t>elc_won_006</t>
@@ -1243,96 +1321,96 @@
     <t>e_w967849373-220,e_w548869165-230,e_w548869165-220,e_w773079147-220,e_VN1164-500,e_VN1130-500</t>
   </si>
   <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_VN374-500,e_VN390-500,e_VN375-220,e_VN441-500,e_w630750798-500,e_VN467-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_VN648-500,e_VN753-220,e_VN714-220,e_VN702-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_VN1206-220,e_VN1186-220,e_w548970109-220,e_VN1188-220</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w1240393348-220</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_VN623-500,e_w1258175914-220,e_w1272088369-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w548970103-220,e_w548970101-220,e_w549005377-220,e_w827889600-220,e_w1052065872-220,e_w744217936-220,e_w548752026-220,e_VN1099-500,e_w1273948690-220,e_w400482074-220,e_w1273948701-220</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w1036283936-220,e_VN118-500,e_w483057097-220,e_VN152-500,e_w469414362-220,e_VN3-220,e_VN167-220,e_w1240393348-220,e_w827889590-500,e_w1245195233-220</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_VN1206-220,e_w548970103-220,e_VN1227-220,e_w548970118-220,e_VN1207-500,e_VN1210-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_VN537-220,e_VN522-500,e_w549400051-220,e_VN575-220</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_VN488-220,e_VN471-500,e_VN512-500,e_w401042494-220</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_VN384-500,e_VN447-500,e_VN433-500,e_VN477-500,e_VN464-500,e_VN457-500,e_VN484-500,e_VN476-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_VN345-220,e_VN324-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w1273328710-220,e_VN738-500,e_w549380074-220,e_VN832-500,e_w400413521-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN770-500,e_VN748-500,e_VN728-220,e_VN695-220,e_w1273898576-220,e_w400474243-220,e_VN988-220,e_w1273527149-220</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_021</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_015</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 15</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
@@ -1351,52 +1429,16 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wofelc_wof_019</t>
@@ -1411,60 +1453,93 @@
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>elc_wof_021</t>
   </si>
   <si>
     <t>e_VN446-500,e_VN410-220,e_VN468-500,e_w1087113517-220,e_w1183902227-500</t>
   </si>
   <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w548970103-220</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w1374565925-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_VN994-500,e_w549038673-220,e_w1274466549-220</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w548970103-220,e_w548970101-220,e_w827889600-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_w548752026-220,e_w548723124-220,e_w1273948690-220,e_w1273948701-220,e_VN1016-500,e_w548717060-500,e_VN1003-500,e_VN988-220,e_w549038673-220,e_VN999-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w549400051-220,e_w1374565925-220</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_w1272088369-220,e_w549400051-220,e_w1258175914-220</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_VN516-500,e_w1374565925-220</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_w1272088369-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_VN1003-500,e_VN999-500,e_VN988-220,e_w1091686589-220</t>
+  </si>
+  <si>
     <t>elc_wof_015</t>
   </si>
   <si>
     <t>e_w401042494-220,e_VN516-500</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w548970101-220,e_w827889600-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_w630750798-220,e_w1320784083-500,e_VN410-220,e_w630750798-500,e_w1183902227-500</t>
+  </si>
+  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
@@ -1483,52 +1558,16 @@
     <t>e_w1272088369-220,e_w1258175914-220,e_w549400051-220</t>
   </si>
   <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_w548752026-220,e_w548723124-220,e_w1273948690-220,e_w1273948701-220,e_VN1016-500,e_w548717060-500,e_VN1003-500,e_VN988-220,e_w549038673-220,e_VN999-500</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w549400051-220,e_w1374565925-220</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_w1272088369-220,e_w549400051-220,e_w1258175914-220</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w548970103-220</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w1374565925-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_w630750798-220,e_w1320784083-500,e_VN410-220,e_w630750798-500,e_w1183902227-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w1272088369-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_VN1003-500,e_VN999-500,e_VN988-220,e_w1091686589-220</t>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w827889600-500,e_VN1228-220,e_VN1145-220</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>e_w436002389-220,e_VN470-500,e_w1183902227-500,e_w401042494-220,e_VN471-500,e_w1087113517-220,e_VN516-500</t>
   </si>
   <si>
     <t>elc_wof_019</t>
@@ -1541,45 +1580,6 @@
   </si>
   <si>
     <t>e_w715041211-220,e_w1245195233-220</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w827889600-500,e_VN1228-220,e_VN1145-220</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_w436002389-220,e_VN470-500,e_w1183902227-500,e_w401042494-220,e_VN471-500,e_w1087113517-220,e_VN516-500</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w548970103-220,e_w548970101-220,e_w827889600-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_VN516-500,e_w1374565925-220</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_VN994-500,e_w549038673-220,e_w1274466549-220</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w548970101-220,e_w827889600-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -8279,7 +8279,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3557EE-DDE7-4E2C-B50F-259A77777F6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0088EF8-6BF3-4903-81BA-3750E1051D66}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8559,10 +8559,10 @@
         <v>364</v>
       </c>
       <c r="AO11">
-        <v>0.99898558640402924</v>
+        <v>0.9975164323387431</v>
       </c>
       <c r="AP11">
-        <v>18.597582592797586</v>
+        <v>45.532073789710303</v>
       </c>
       <c r="AR11" t="s">
         <v>252</v>
@@ -8705,10 +8705,10 @@
         <v>366</v>
       </c>
       <c r="AO12">
-        <v>0.9982523129285531</v>
+        <v>0.99938105508849573</v>
       </c>
       <c r="AP12">
-        <v>32.040929643194062</v>
+        <v>11.34732337757792</v>
       </c>
       <c r="AR12" t="s">
         <v>252</v>
@@ -8741,10 +8741,10 @@
         <v>444</v>
       </c>
       <c r="BC12">
-        <v>0.99497940415328234</v>
+        <v>0.98791946624258509</v>
       </c>
       <c r="BD12">
-        <v>92.044257189823469</v>
+        <v>221.4764522192738</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8851,10 +8851,10 @@
         <v>368</v>
       </c>
       <c r="AO13">
-        <v>0.99938105508849573</v>
+        <v>0.99881597306370296</v>
       </c>
       <c r="AP13">
-        <v>11.34732337757792</v>
+        <v>21.707160498778528</v>
       </c>
       <c r="AR13" t="s">
         <v>252</v>
@@ -8887,10 +8887,10 @@
         <v>446</v>
       </c>
       <c r="BC13">
-        <v>0.98009770506351668</v>
+        <v>0.99509603189170837</v>
       </c>
       <c r="BD13">
-        <v>364.87540716886002</v>
+        <v>89.90608198534612</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8997,10 +8997,10 @@
         <v>370</v>
       </c>
       <c r="AO14">
-        <v>0.99844423111858249</v>
+        <v>0.9982523129285531</v>
       </c>
       <c r="AP14">
-        <v>28.522429492654361</v>
+        <v>32.040929643194062</v>
       </c>
       <c r="AR14" t="s">
         <v>252</v>
@@ -9033,10 +9033,10 @@
         <v>448</v>
       </c>
       <c r="BC14">
-        <v>0.9969294297150163</v>
+        <v>0.99560758626248369</v>
       </c>
       <c r="BD14">
-        <v>56.2937885580344</v>
+        <v>80.527585187798735</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9101,16 +9101,16 @@
         <v>263</v>
       </c>
       <c r="Y15" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="Z15" t="s">
         <v>309</v>
       </c>
       <c r="AA15">
-        <v>0.99841532396070098</v>
+        <v>0.99916935310675503</v>
       </c>
       <c r="AB15">
-        <v>29.052394053816059</v>
+        <v>15.22852637615807</v>
       </c>
       <c r="AD15" t="s">
         <v>252</v>
@@ -9143,10 +9143,10 @@
         <v>372</v>
       </c>
       <c r="AO15">
-        <v>0.99907918970282927</v>
+        <v>0.99766805126871516</v>
       </c>
       <c r="AP15">
-        <v>16.881522114796713</v>
+        <v>42.752393406888629</v>
       </c>
       <c r="AR15" t="s">
         <v>252</v>
@@ -9179,10 +9179,10 @@
         <v>450</v>
       </c>
       <c r="BC15">
-        <v>0.99534342454901092</v>
+        <v>0.98877515176124608</v>
       </c>
       <c r="BD15">
-        <v>85.370549934800536</v>
+        <v>205.78888437715531</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9247,16 +9247,16 @@
         <v>265</v>
       </c>
       <c r="Y16" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="Z16" t="s">
         <v>310</v>
       </c>
       <c r="AA16">
-        <v>0.99748798960410945</v>
+        <v>0.99838245441178075</v>
       </c>
       <c r="AB16">
-        <v>46.05352392465965</v>
+        <v>29.65500245068538</v>
       </c>
       <c r="AD16" t="s">
         <v>252</v>
@@ -9393,16 +9393,16 @@
         <v>267</v>
       </c>
       <c r="Y17" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Z17" t="s">
         <v>311</v>
       </c>
       <c r="AA17">
-        <v>0.99853082183379016</v>
+        <v>0.99841532396070098</v>
       </c>
       <c r="AB17">
-        <v>26.934933047180987</v>
+        <v>29.052394053816059</v>
       </c>
       <c r="AD17" t="s">
         <v>252</v>
@@ -9435,10 +9435,10 @@
         <v>376</v>
       </c>
       <c r="AO17">
-        <v>0.99796388855873064</v>
+        <v>0.99926426412261371</v>
       </c>
       <c r="AP17">
-        <v>37.328709756605285</v>
+        <v>13.488491085415317</v>
       </c>
       <c r="AR17" t="s">
         <v>252</v>
@@ -9539,16 +9539,16 @@
         <v>269</v>
       </c>
       <c r="Y18" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="Z18" t="s">
         <v>312</v>
       </c>
       <c r="AA18">
-        <v>0.99886029773300145</v>
+        <v>0.99748798960410945</v>
       </c>
       <c r="AB18">
-        <v>20.894541561640985</v>
+        <v>46.05352392465965</v>
       </c>
       <c r="AD18" t="s">
         <v>252</v>
@@ -9581,10 +9581,10 @@
         <v>378</v>
       </c>
       <c r="AO18">
-        <v>0.995847998099891</v>
+        <v>0.99911920301541846</v>
       </c>
       <c r="AP18">
-        <v>76.120034835332021</v>
+        <v>16.147944717327473</v>
       </c>
       <c r="AR18" t="s">
         <v>252</v>
@@ -9685,16 +9685,16 @@
         <v>271</v>
       </c>
       <c r="Y19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Z19" t="s">
         <v>313</v>
       </c>
       <c r="AA19">
-        <v>0.99853654721508034</v>
+        <v>0.99853082183379016</v>
       </c>
       <c r="AB19">
-        <v>26.829967723528117</v>
+        <v>26.934933047180987</v>
       </c>
       <c r="AD19" t="s">
         <v>252</v>
@@ -9727,10 +9727,10 @@
         <v>380</v>
       </c>
       <c r="AO19">
-        <v>0.99837166789655962</v>
+        <v>0.99796388855873064</v>
       </c>
       <c r="AP19">
-        <v>29.852755229741184</v>
+        <v>37.328709756605285</v>
       </c>
       <c r="AR19" t="s">
         <v>252</v>
@@ -9760,13 +9760,13 @@
         <v>457</v>
       </c>
       <c r="BB19" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="BC19">
-        <v>0.98791946624258509</v>
+        <v>0.98389971341016413</v>
       </c>
       <c r="BD19">
-        <v>221.4764522192738</v>
+        <v>295.17192081365857</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9831,16 +9831,16 @@
         <v>273</v>
       </c>
       <c r="Y20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Z20" t="s">
         <v>314</v>
       </c>
       <c r="AA20">
-        <v>0.99908330527279288</v>
+        <v>0.99886029773300145</v>
       </c>
       <c r="AB20">
-        <v>16.806069998796339</v>
+        <v>20.894541561640985</v>
       </c>
       <c r="AD20" t="s">
         <v>252</v>
@@ -9873,10 +9873,10 @@
         <v>382</v>
       </c>
       <c r="AO20">
-        <v>0.99887560286820065</v>
+        <v>0.995847998099891</v>
       </c>
       <c r="AP20">
-        <v>20.613947416322183</v>
+        <v>76.120034835332021</v>
       </c>
       <c r="AR20" t="s">
         <v>252</v>
@@ -9903,16 +9903,16 @@
         <v>415</v>
       </c>
       <c r="BA20" t="s">
+        <v>458</v>
+      </c>
+      <c r="BB20" t="s">
         <v>459</v>
       </c>
-      <c r="BB20" t="s">
-        <v>460</v>
-      </c>
       <c r="BC20">
-        <v>0.99509603189170837</v>
+        <v>0.99068186135163905</v>
       </c>
       <c r="BD20">
-        <v>89.90608198534612</v>
+        <v>170.83254188661647</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9977,16 +9977,16 @@
         <v>275</v>
       </c>
       <c r="Y21" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="Z21" t="s">
         <v>315</v>
       </c>
       <c r="AA21">
-        <v>0.99925831158204348</v>
+        <v>0.99881634769332572</v>
       </c>
       <c r="AB21">
-        <v>13.597620995868882</v>
+        <v>21.700292289029083</v>
       </c>
       <c r="AD21" t="s">
         <v>252</v>
@@ -10019,10 +10019,10 @@
         <v>384</v>
       </c>
       <c r="AO21">
-        <v>0.99766805126871516</v>
+        <v>0.99837166789655962</v>
       </c>
       <c r="AP21">
-        <v>42.752393406888629</v>
+        <v>29.852755229741184</v>
       </c>
       <c r="AR21" t="s">
         <v>252</v>
@@ -10049,16 +10049,16 @@
         <v>417</v>
       </c>
       <c r="BA21" t="s">
+        <v>460</v>
+      </c>
+      <c r="BB21" t="s">
         <v>461</v>
       </c>
-      <c r="BB21" t="s">
-        <v>462</v>
-      </c>
       <c r="BC21">
-        <v>0.99345827826480626</v>
+        <v>0.98020101972536366</v>
       </c>
       <c r="BD21">
-        <v>119.93156514521847</v>
+        <v>362.98130503499954</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10123,16 +10123,16 @@
         <v>277</v>
       </c>
       <c r="Y22" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Z22" t="s">
         <v>316</v>
       </c>
       <c r="AA22">
-        <v>0.99881634769332572</v>
+        <v>0.99902825268538287</v>
       </c>
       <c r="AB22">
-        <v>21.700292289029083</v>
+        <v>17.815367434646582</v>
       </c>
       <c r="AD22" t="s">
         <v>252</v>
@@ -10195,16 +10195,16 @@
         <v>419</v>
       </c>
       <c r="BA22" t="s">
+        <v>462</v>
+      </c>
+      <c r="BB22" t="s">
         <v>463</v>
       </c>
-      <c r="BB22" t="s">
-        <v>464</v>
-      </c>
       <c r="BC22">
-        <v>0.98020101972536366</v>
+        <v>0.97141625641711749</v>
       </c>
       <c r="BD22">
-        <v>362.98130503499954</v>
+        <v>524.03529901951276</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10269,16 +10269,16 @@
         <v>279</v>
       </c>
       <c r="Y23" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="Z23" t="s">
         <v>317</v>
       </c>
       <c r="AA23">
-        <v>0.99902825268538287</v>
+        <v>0.99748113422069817</v>
       </c>
       <c r="AB23">
-        <v>17.815367434646582</v>
+        <v>46.179205953867658</v>
       </c>
       <c r="AD23" t="s">
         <v>252</v>
@@ -10341,16 +10341,16 @@
         <v>421</v>
       </c>
       <c r="BA23" t="s">
+        <v>464</v>
+      </c>
+      <c r="BB23" t="s">
         <v>465</v>
       </c>
-      <c r="BB23" t="s">
-        <v>466</v>
-      </c>
       <c r="BC23">
-        <v>0.97141625641711749</v>
+        <v>0.99497940415328234</v>
       </c>
       <c r="BD23">
-        <v>524.03529901951276</v>
+        <v>92.044257189823469</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10415,16 +10415,16 @@
         <v>281</v>
       </c>
       <c r="Y24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Z24" t="s">
         <v>318</v>
       </c>
       <c r="AA24">
-        <v>0.99790242535065354</v>
+        <v>0.9968034818648015</v>
       </c>
       <c r="AB24">
-        <v>38.455535238019358</v>
+        <v>58.602832478639002</v>
       </c>
       <c r="AD24" t="s">
         <v>252</v>
@@ -10457,10 +10457,10 @@
         <v>390</v>
       </c>
       <c r="AO24">
-        <v>0.99881597306370296</v>
+        <v>0.99907918970282927</v>
       </c>
       <c r="AP24">
-        <v>21.707160498778528</v>
+        <v>16.881522114796713</v>
       </c>
       <c r="AR24" t="s">
         <v>252</v>
@@ -10487,16 +10487,16 @@
         <v>423</v>
       </c>
       <c r="BA24" t="s">
+        <v>466</v>
+      </c>
+      <c r="BB24" t="s">
         <v>467</v>
       </c>
-      <c r="BB24" t="s">
-        <v>468</v>
-      </c>
       <c r="BC24">
-        <v>0.99160116355990502</v>
+        <v>0.97765588244922996</v>
       </c>
       <c r="BD24">
-        <v>153.97866806840764</v>
+        <v>409.64215509745077</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10561,16 +10561,16 @@
         <v>283</v>
       </c>
       <c r="Y25" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="Z25" t="s">
         <v>319</v>
       </c>
       <c r="AA25">
-        <v>0.99922833574773007</v>
+        <v>0.99544314722299798</v>
       </c>
       <c r="AB25">
-        <v>14.14717795828226</v>
+        <v>83.542300911704686</v>
       </c>
       <c r="AD25" t="s">
         <v>252</v>
@@ -10603,10 +10603,10 @@
         <v>392</v>
       </c>
       <c r="AO25">
-        <v>0.9975164323387431</v>
+        <v>0.99898558640402924</v>
       </c>
       <c r="AP25">
-        <v>45.532073789710303</v>
+        <v>18.597582592797586</v>
       </c>
       <c r="AR25" t="s">
         <v>252</v>
@@ -10633,16 +10633,16 @@
         <v>425</v>
       </c>
       <c r="BA25" t="s">
+        <v>468</v>
+      </c>
+      <c r="BB25" t="s">
         <v>469</v>
       </c>
-      <c r="BB25" t="s">
-        <v>470</v>
-      </c>
       <c r="BC25">
-        <v>0.99255179421932938</v>
+        <v>0.99345827826480626</v>
       </c>
       <c r="BD25">
-        <v>136.55043931229389</v>
+        <v>119.93156514521847</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10707,16 +10707,16 @@
         <v>285</v>
       </c>
       <c r="Y26" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Z26" t="s">
         <v>320</v>
       </c>
       <c r="AA26">
-        <v>0.99930751773166338</v>
+        <v>0.99790242535065354</v>
       </c>
       <c r="AB26">
-        <v>12.695508252837362</v>
+        <v>38.455535238019358</v>
       </c>
       <c r="AD26" t="s">
         <v>252</v>
@@ -10749,10 +10749,10 @@
         <v>394</v>
       </c>
       <c r="AO26">
-        <v>0.99926426412261371</v>
+        <v>0.99887560286820065</v>
       </c>
       <c r="AP26">
-        <v>13.488491085415317</v>
+        <v>20.613947416322183</v>
       </c>
       <c r="AR26" t="s">
         <v>252</v>
@@ -10779,16 +10779,16 @@
         <v>427</v>
       </c>
       <c r="BA26" t="s">
+        <v>470</v>
+      </c>
+      <c r="BB26" t="s">
         <v>471</v>
       </c>
-      <c r="BB26" t="s">
-        <v>472</v>
-      </c>
       <c r="BC26">
-        <v>0.98627052110774238</v>
+        <v>0.98009770506351668</v>
       </c>
       <c r="BD26">
-        <v>251.70711302472259</v>
+        <v>364.87540716886002</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10853,16 +10853,16 @@
         <v>287</v>
       </c>
       <c r="Y27" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="Z27" t="s">
         <v>321</v>
       </c>
       <c r="AA27">
-        <v>0.99544370356555212</v>
+        <v>0.99922833574773007</v>
       </c>
       <c r="AB27">
-        <v>83.53210129821079</v>
+        <v>14.14717795828226</v>
       </c>
       <c r="AD27" t="s">
         <v>252</v>
@@ -10895,10 +10895,10 @@
         <v>396</v>
       </c>
       <c r="AO27">
-        <v>0.99911920301541846</v>
+        <v>0.99844423111858249</v>
       </c>
       <c r="AP27">
-        <v>16.147944717327473</v>
+        <v>28.522429492654361</v>
       </c>
       <c r="AR27" t="s">
         <v>252</v>
@@ -10925,16 +10925,16 @@
         <v>429</v>
       </c>
       <c r="BA27" t="s">
+        <v>472</v>
+      </c>
+      <c r="BB27" t="s">
         <v>473</v>
       </c>
-      <c r="BB27" t="s">
-        <v>474</v>
-      </c>
       <c r="BC27">
-        <v>0.99278784076394344</v>
+        <v>0.9969294297150163</v>
       </c>
       <c r="BD27">
-        <v>132.22291932770449</v>
+        <v>56.2937885580344</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10999,16 +10999,16 @@
         <v>289</v>
       </c>
       <c r="Y28" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Z28" t="s">
         <v>322</v>
       </c>
       <c r="AA28">
-        <v>0.99874244650354715</v>
+        <v>0.99897010067703429</v>
       </c>
       <c r="AB28">
-        <v>23.055147434969136</v>
+        <v>18.881487587705607</v>
       </c>
       <c r="AR28" t="s">
         <v>252</v>
@@ -11035,16 +11035,16 @@
         <v>431</v>
       </c>
       <c r="BA28" t="s">
+        <v>474</v>
+      </c>
+      <c r="BB28" t="s">
         <v>475</v>
       </c>
-      <c r="BB28" t="s">
-        <v>476</v>
-      </c>
       <c r="BC28">
-        <v>0.98877515176124608</v>
+        <v>0.99534342454901092</v>
       </c>
       <c r="BD28">
-        <v>205.78888437715531</v>
+        <v>85.370549934800536</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11109,16 +11109,16 @@
         <v>291</v>
       </c>
       <c r="Y29" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="Z29" t="s">
         <v>323</v>
       </c>
       <c r="AA29">
-        <v>0.99544314722299798</v>
+        <v>0.99930751773166338</v>
       </c>
       <c r="AB29">
-        <v>83.542300911704686</v>
+        <v>12.695508252837362</v>
       </c>
       <c r="AR29" t="s">
         <v>252</v>
@@ -11145,16 +11145,16 @@
         <v>433</v>
       </c>
       <c r="BA29" t="s">
+        <v>476</v>
+      </c>
+      <c r="BB29" t="s">
         <v>477</v>
       </c>
-      <c r="BB29" t="s">
-        <v>458</v>
-      </c>
       <c r="BC29">
-        <v>0.98389971341016413</v>
+        <v>0.98627052110774238</v>
       </c>
       <c r="BD29">
-        <v>295.17192081365857</v>
+        <v>251.70711302472259</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11219,16 +11219,16 @@
         <v>293</v>
       </c>
       <c r="Y30" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Z30" t="s">
         <v>324</v>
       </c>
       <c r="AA30">
-        <v>0.99748113422069817</v>
+        <v>0.99544370356555212</v>
       </c>
       <c r="AB30">
-        <v>46.179205953867658</v>
+        <v>83.53210129821079</v>
       </c>
       <c r="AR30" t="s">
         <v>252</v>
@@ -11261,10 +11261,10 @@
         <v>479</v>
       </c>
       <c r="BC30">
-        <v>0.99068186135163905</v>
+        <v>0.99278784076394344</v>
       </c>
       <c r="BD30">
-        <v>170.83254188661647</v>
+        <v>132.22291932770449</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11329,16 +11329,16 @@
         <v>295</v>
       </c>
       <c r="Y31" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="Z31" t="s">
         <v>325</v>
       </c>
       <c r="AA31">
-        <v>0.9968034818648015</v>
+        <v>0.99874244650354715</v>
       </c>
       <c r="AB31">
-        <v>58.602832478639002</v>
+        <v>23.055147434969136</v>
       </c>
       <c r="AR31" t="s">
         <v>252</v>
@@ -11371,10 +11371,10 @@
         <v>481</v>
       </c>
       <c r="BC31">
-        <v>0.99560758626248369</v>
+        <v>0.99160116355990502</v>
       </c>
       <c r="BD31">
-        <v>80.527585187798735</v>
+        <v>153.97866806840764</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11439,16 +11439,16 @@
         <v>297</v>
       </c>
       <c r="Y32" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Z32" t="s">
         <v>326</v>
       </c>
       <c r="AA32">
-        <v>0.99916935310675503</v>
+        <v>0.99853654721508034</v>
       </c>
       <c r="AB32">
-        <v>15.22852637615807</v>
+        <v>26.829967723528117</v>
       </c>
       <c r="AR32" t="s">
         <v>252</v>
@@ -11481,10 +11481,10 @@
         <v>483</v>
       </c>
       <c r="BC32">
-        <v>0.97765588244922996</v>
+        <v>0.99255179421932938</v>
       </c>
       <c r="BD32">
-        <v>409.64215509745077</v>
+        <v>136.55043931229389</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -11549,16 +11549,16 @@
         <v>299</v>
       </c>
       <c r="Y33" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Z33" t="s">
         <v>327</v>
       </c>
       <c r="AA33">
-        <v>0.99838245441178075</v>
+        <v>0.99908330527279288</v>
       </c>
       <c r="AB33">
-        <v>29.65500245068538</v>
+        <v>16.806069998796339</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -11623,16 +11623,16 @@
         <v>301</v>
       </c>
       <c r="Y34" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="Z34" t="s">
         <v>328</v>
       </c>
       <c r="AA34">
-        <v>0.99897010067703429</v>
+        <v>0.99925831158204348</v>
       </c>
       <c r="AB34">
-        <v>18.881487587705607</v>
+        <v>13.597620995868882</v>
       </c>
     </row>
   </sheetData>
@@ -11641,7 +11641,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F71BBBC-9AF5-48B3-B084-8CB2366C7782}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6F5AF5-AE10-4B03-AB82-BBEF6D72383B}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11753,7 +11753,7 @@
         <v>484</v>
       </c>
       <c r="K11" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="L11">
         <v>9.9561879268440521</v>
@@ -11786,7 +11786,7 @@
         <v>518</v>
       </c>
       <c r="X11" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="Y11">
         <v>5.7030000000000003</v>
@@ -11821,7 +11821,7 @@
         <v>486</v>
       </c>
       <c r="K12" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L12">
         <v>15.610469208056319</v>
@@ -11854,7 +11854,7 @@
         <v>520</v>
       </c>
       <c r="X12" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="Y12">
         <v>3.2370000000000001</v>
@@ -11889,7 +11889,7 @@
         <v>488</v>
       </c>
       <c r="K13" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="L13">
         <v>38.93604588989777</v>
@@ -11922,7 +11922,7 @@
         <v>522</v>
       </c>
       <c r="X13" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="Y13">
         <v>0.73950000000000005</v>
@@ -11957,7 +11957,7 @@
         <v>490</v>
       </c>
       <c r="K14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L14">
         <v>3.4061833906252343</v>
@@ -11990,7 +11990,7 @@
         <v>524</v>
       </c>
       <c r="X14" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="Y14">
         <v>17.418749999999999</v>
@@ -12025,7 +12025,7 @@
         <v>492</v>
       </c>
       <c r="K15" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="L15">
         <v>10.05531955531686</v>
@@ -12093,7 +12093,7 @@
         <v>494</v>
       </c>
       <c r="K16" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="L16">
         <v>11.000319473014851</v>
@@ -12126,7 +12126,7 @@
         <v>528</v>
       </c>
       <c r="X16" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="Y16">
         <v>26.099250000000001</v>
@@ -12161,7 +12161,7 @@
         <v>496</v>
       </c>
       <c r="K17" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="L17">
         <v>1.9758785540112649</v>
@@ -12194,7 +12194,7 @@
         <v>530</v>
       </c>
       <c r="X17" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="Y17">
         <v>6.7657499999999997</v>
@@ -12262,7 +12262,7 @@
         <v>532</v>
       </c>
       <c r="X18" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="Y18">
         <v>18.204750000000001</v>
@@ -12330,7 +12330,7 @@
         <v>534</v>
       </c>
       <c r="X19" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="Y19">
         <v>53.964750000000002</v>
@@ -12365,7 +12365,7 @@
         <v>502</v>
       </c>
       <c r="K20" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L20">
         <v>7.8234985450080243</v>
@@ -12398,7 +12398,7 @@
         <v>536</v>
       </c>
       <c r="X20" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="Y20">
         <v>32.474249999999998</v>
@@ -12433,7 +12433,7 @@
         <v>504</v>
       </c>
       <c r="K21" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="L21">
         <v>35.48135454794123</v>
@@ -12466,7 +12466,7 @@
         <v>538</v>
       </c>
       <c r="X21" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="Y21">
         <v>24.771750000000001</v>
@@ -12501,7 +12501,7 @@
         <v>506</v>
       </c>
       <c r="K22" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="L22">
         <v>31.11916467188631</v>
@@ -12569,7 +12569,7 @@
         <v>508</v>
       </c>
       <c r="K23" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="L23">
         <v>4.5001608244833662</v>
@@ -12637,7 +12637,7 @@
         <v>510</v>
       </c>
       <c r="K24" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="L24">
         <v>9.5500952124569967</v>
@@ -12670,7 +12670,7 @@
         <v>544</v>
       </c>
       <c r="X24" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="Y24">
         <v>38.413499999999999</v>
@@ -12705,7 +12705,7 @@
         <v>512</v>
       </c>
       <c r="K25" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L25">
         <v>5.3426370365388722</v>
@@ -12738,7 +12738,7 @@
         <v>546</v>
       </c>
       <c r="X25" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="Y25">
         <v>15.254250000000001</v>
@@ -12806,7 +12806,7 @@
         <v>548</v>
       </c>
       <c r="X26" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="Y26">
         <v>16.820250000000001</v>
@@ -12841,7 +12841,7 @@
         <v>516</v>
       </c>
       <c r="K27" t="s">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="L27">
         <v>0.94607061901700107</v>
@@ -12874,7 +12874,7 @@
         <v>550</v>
       </c>
       <c r="X27" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="Y27">
         <v>32.364750000000001</v>
@@ -12909,7 +12909,7 @@
         <v>552</v>
       </c>
       <c r="X28" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="Y28">
         <v>20.224499999999999</v>
@@ -12944,7 +12944,7 @@
         <v>554</v>
       </c>
       <c r="X29" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="Y29">
         <v>13.347</v>
@@ -12979,7 +12979,7 @@
         <v>556</v>
       </c>
       <c r="X30" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="Y30">
         <v>3.7177500000000001</v>
@@ -13049,7 +13049,7 @@
         <v>560</v>
       </c>
       <c r="X32" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="Y32">
         <v>38.509500000000003</v>
@@ -13064,7 +13064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8F0129-A7EC-44FB-A868-9F64DE6ABDDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42102259-BD5B-4C56-9C54-94497EB7F7B9}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14881,7 +14881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDAB4CB7-0B5B-4F0F-9030-C411AE47E7C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF37CA50-39BE-41DD-8D4E-E2B6A90143A6}">
   <dimension ref="B2:M187"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_VNM_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_VNM_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DDB00D5-8D3C-4F91-9C2F-E9243422ED26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCBAB7C1-30BE-43C5-BFF8-0FCD584898D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -931,6 +931,78 @@
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_007</t>
   </si>
   <si>
@@ -955,18 +1027,6 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_018</t>
   </si>
   <si>
@@ -979,66 +1039,6 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1063,6 +1063,42 @@
     <t>e_VN477-500,e_VN464-500,e_VN484-500,e_VN476-500,e_VN467-500,e_VN569-220,e_VN510-220,e_VN488-220,e_VN471-500</t>
   </si>
   <si>
+    <t>e_VN1130-500,e_w1051605925-220,e_w775832889-220,e_VN1156-500,e_w1052403240-220,e_VN983-220,e_w1176845159-220,e_VN1154-220,e_VN1097-220,e_VN987-500,e_VN930-500,e_VN918-500,e_w1212041269-220,e_VN1017-500</t>
+  </si>
+  <si>
+    <t>e_w1050835279-220,e_VN278-500,e_VN235-500,e_VN321-220,e_w857794232-220,e_VN280-500</t>
+  </si>
+  <si>
+    <t>e_w439941742-220,e_VN556-500,e_VN512-500,e_w401042494-220,e_w1233471417-220,e_VN585-500,e_VN537-220,e_VN522-500,e_w1258175914-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>e_VN321-220,e_w1267181647-220,e_VN297-500,e_VN128-500,e_VN324-500,e_VN322-220,e_VN314-500,e_VN256-220,e_w1320784083-500,e_VN320-220,e_VN312-220,e_w1036283936-220,e_w750907640-220</t>
+  </si>
+  <si>
+    <t>e_VN3-220,e_w1240393348-220</t>
+  </si>
+  <si>
+    <t>e_VN738-500,e_w549380074-220,e_w401532710-220,e_VN624-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN644-500</t>
+  </si>
+  <si>
+    <t>e_VN310-220,e_w1045125739-220,e_VN152-500,e_w469414362-220,e_w241065371-220,e_VN167-220,e_w827889590-500,e_w1245195233-220</t>
+  </si>
+  <si>
+    <t>e_VN614-220,e_VN590-220,e_VN611-500,e_VN728-220,e_VN695-220,e_VN648-500,e_VN702-220,e_VN623-500,e_w1272088369-220</t>
+  </si>
+  <si>
+    <t>e_VN390-500,e_VN375-220,e_VN457-500,e_VN441-500,e_w630750798-500</t>
+  </si>
+  <si>
+    <t>e_w1050835279-220,e_VN351-220</t>
+  </si>
+  <si>
+    <t>e_w548970103-220,e_w548970101-220,e_VN1227-220,e_VN1207-500,e_w549005377-220,e_VN1210-500,e_w827889600-220,e_w1052065872-220,e_w744217936-220</t>
+  </si>
+  <si>
+    <t>e_VN900-500,e_VN855-500,e_w1273328710-220,e_VN1013-220,e_VN907-220,e_VN832-500,e_w400413521-220,e_w400482074-220,e_VN920-500,e_VN816-500</t>
+  </si>
+  <si>
     <t>e_VN1206-220,e_VN1186-220,e_w548970103-220,e_w548970109-220,e_VN1188-220,e_w967849373-220,e_VN1227-220,e_w548970118-220,e_w548869165-230,e_w548869165-220,e_w773079147-220,e_VN1164-500</t>
   </si>
   <si>
@@ -1075,46 +1111,88 @@
     <t>e_VN770-500,e_VN748-500,e_VN844-500,e_VN753-220,e_VN714-220,e_VN836-220,e_w1273255944-220,e_w549197475-220,e_w549296358-220</t>
   </si>
   <si>
-    <t>e_w548970103-220,e_w548970101-220,e_VN1227-220,e_VN1207-500,e_w549005377-220,e_VN1210-500,e_w827889600-220,e_w1052065872-220,e_w744217936-220</t>
-  </si>
-  <si>
-    <t>e_VN900-500,e_VN855-500,e_w1273328710-220,e_VN1013-220,e_VN907-220,e_VN832-500,e_w400413521-220,e_w400482074-220,e_VN920-500,e_VN816-500</t>
-  </si>
-  <si>
     <t>e_VN8-500,e_w893223532-220,e_VN16-500,e_VN15-500,e_w1263573984-220,e_VN2-220</t>
   </si>
   <si>
     <t>e_VN367-500,e_VN384-500,e_VN374-500,e_VN447-500,e_VN433-500</t>
   </si>
   <si>
-    <t>e_w1050835279-220,e_VN351-220</t>
-  </si>
-  <si>
-    <t>e_w1050835279-220,e_VN278-500,e_VN235-500,e_VN321-220,e_w857794232-220,e_VN280-500</t>
-  </si>
-  <si>
-    <t>e_w439941742-220,e_VN556-500,e_VN512-500,e_w401042494-220,e_w1233471417-220,e_VN585-500,e_VN537-220,e_VN522-500,e_w1258175914-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>e_VN1130-500,e_w1051605925-220,e_w775832889-220,e_VN1156-500,e_w1052403240-220,e_VN983-220,e_w1176845159-220,e_VN1154-220,e_VN1097-220,e_VN987-500,e_VN930-500,e_VN918-500,e_w1212041269-220,e_VN1017-500</t>
-  </si>
-  <si>
-    <t>e_VN321-220,e_w1267181647-220,e_VN297-500,e_VN128-500,e_VN324-500,e_VN322-220,e_VN314-500,e_VN256-220,e_w1320784083-500,e_VN320-220,e_VN312-220,e_w1036283936-220,e_w750907640-220</t>
-  </si>
-  <si>
-    <t>e_VN3-220,e_w1240393348-220</t>
-  </si>
-  <si>
-    <t>e_VN738-500,e_w549380074-220,e_w401532710-220,e_VN624-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN644-500</t>
-  </si>
-  <si>
-    <t>e_VN310-220,e_w1045125739-220,e_VN152-500,e_w469414362-220,e_w241065371-220,e_VN167-220,e_w827889590-500,e_w1245195233-220</t>
-  </si>
-  <si>
-    <t>e_VN614-220,e_VN590-220,e_VN611-500,e_VN728-220,e_VN695-220,e_VN648-500,e_VN702-220,e_VN623-500,e_w1272088369-220</t>
-  </si>
-  <si>
-    <t>e_VN390-500,e_VN375-220,e_VN457-500,e_VN441-500,e_w630750798-500</t>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wonelc_won_012</t>
@@ -1123,10 +1201,16 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wonelc_won_017</t>
@@ -1135,88 +1219,82 @@
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_VN1206-220,e_VN1186-220,e_w548970109-220,e_VN1188-220</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w1240393348-220</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_VN623-500,e_w1258175914-220,e_w1272088369-220</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w1036283936-220,e_VN118-500,e_w483057097-220,e_VN152-500,e_w469414362-220,e_VN3-220,e_VN167-220,e_w1240393348-220,e_w827889590-500,e_w1245195233-220</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w775832889-220,e_VN918-500,e_VN900-500,e_VN855-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_VN1206-220,e_w548970103-220,e_VN1227-220,e_w548970118-220,e_VN1207-500,e_VN1210-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_VN537-220,e_VN522-500,e_w549400051-220,e_VN575-220</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w1320784083-500,e_VN320-220,e_VN312-220,e_w750907640-220,e_VN310-220,e_w1045125739-220,e_w241065371-220,e_w715041211-220,e_w1245195233-220</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_VN1156-500,e_VN1154-220,e_VN1152-220</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w967849373-220,e_w548869165-230,e_w548869165-220,e_w773079147-220,e_VN1164-500,e_VN1130-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w548970103-220,e_w548970101-220,e_w549005377-220,e_w827889600-220,e_w1052065872-220,e_w744217936-220,e_w548752026-220,e_VN1099-500,e_w1273948690-220,e_w400482074-220,e_w1273948701-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_VN345-220,e_VN324-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w1273328710-220,e_VN738-500,e_w549380074-220,e_VN832-500,e_w400413521-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN770-500,e_VN748-500,e_VN728-220,e_VN695-220,e_w1273898576-220,e_w400474243-220,e_VN988-220,e_w1273527149-220</t>
   </si>
   <si>
     <t>elc_won_012</t>
@@ -1225,10 +1303,16 @@
     <t>e_VN384-500,e_VN447-500,e_VN433-500,e_VN477-500,e_VN464-500,e_VN457-500,e_VN484-500,e_VN476-500</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_VN1156-500,e_VN1154-220,e_VN1152-220</t>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_VN648-500,e_VN753-220,e_VN714-220,e_VN702-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_VN374-500,e_VN390-500,e_VN375-220,e_VN441-500,e_w630750798-500,e_VN467-500</t>
   </si>
   <si>
     <t>elc_won_017</t>
@@ -1237,88 +1321,40 @@
     <t>e_VN488-220,e_VN471-500,e_VN512-500,e_w401042494-220</t>
   </si>
   <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w775832889-220,e_VN918-500,e_VN900-500,e_VN855-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w1036283936-220,e_VN118-500,e_w483057097-220,e_VN152-500,e_w469414362-220,e_VN3-220,e_VN167-220,e_w1240393348-220,e_w827889590-500,e_w1245195233-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_VN648-500,e_VN753-220,e_VN714-220,e_VN702-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_VN345-220,e_VN324-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w1273328710-220,e_VN738-500,e_w549380074-220,e_VN832-500,e_w400413521-220,e_VN746-500,e_VN730-500,e_VN693-500,e_VN770-500,e_VN748-500,e_VN728-220,e_VN695-220,e_w1273898576-220,e_w400474243-220,e_VN988-220,e_w1273527149-220</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_VN1206-220,e_VN1186-220,e_w548970109-220,e_VN1188-220</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w1240393348-220</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_VN623-500,e_w1258175914-220,e_w1272088369-220</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_VN1206-220,e_w548970103-220,e_VN1227-220,e_w548970118-220,e_VN1207-500,e_VN1210-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_VN537-220,e_VN522-500,e_w549400051-220,e_VN575-220</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_VN374-500,e_VN390-500,e_VN375-220,e_VN441-500,e_w630750798-500,e_VN467-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w1320784083-500,e_VN320-220,e_VN312-220,e_w750907640-220,e_VN310-220,e_w1045125739-220,e_w241065371-220,e_w715041211-220,e_w1245195233-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w548970103-220,e_w548970101-220,e_w549005377-220,e_w827889600-220,e_w1052065872-220,e_w744217936-220,e_w548752026-220,e_VN1099-500,e_w1273948690-220,e_w400482074-220,e_w1273948701-220</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w967849373-220,e_w548869165-230,e_w548869165-220,e_w773079147-220,e_VN1164-500,e_VN1130-500</t>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wofelc_wof_021</t>
@@ -1327,16 +1363,64 @@
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wofelc_wof_004</t>
@@ -1345,112 +1429,64 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w548970103-220</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w1374565925-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_w548752026-220,e_w548723124-220,e_w1273948690-220,e_w1273948701-220,e_VN1016-500,e_w548717060-500,e_VN1003-500,e_VN988-220,e_w549038673-220,e_VN999-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w549400051-220,e_w1374565925-220</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_w1272088369-220,e_w549400051-220,e_w1258175914-220</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_w630750798-220,e_w1320784083-500,e_VN410-220,e_w630750798-500,e_w1183902227-500</t>
   </si>
   <si>
     <t>elc_wof_021</t>
@@ -1459,16 +1495,61 @@
     <t>e_VN446-500,e_VN410-220,e_VN468-500,e_w1087113517-220,e_w1183902227-500</t>
   </si>
   <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w548970103-220</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w1374565925-220,e_w549400051-220</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_VN516-500,e_w1374565925-220</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_w1272088369-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_VN1003-500,e_VN999-500,e_VN988-220,e_w1091686589-220</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_VN1228-220,e_w548752026-220,e_w548723124-220,e_w1273948701-220,e_w548717060-500,e_VN1003-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w1273527149-220,e_VN836-220,e_w1273255946-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220,e_w1376430795-500</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_w1272088369-220,e_w1258175914-220,e_w549400051-220</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_w401042494-220,e_VN516-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_w750907640-220,e_w1044469623-220,e_w715041211-220</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_w715041211-220,e_w1245195233-220</t>
   </si>
   <si>
     <t>elc_wof_004</t>
@@ -1477,109 +1558,28 @@
     <t>e_VN994-500,e_w549038673-220,e_w1274466549-220</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w548970101-220,e_w827889600-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w827889600-500,e_VN1228-220,e_VN1145-220</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>e_w436002389-220,e_VN470-500,e_w1183902227-500,e_w401042494-220,e_VN471-500,e_w1087113517-220,e_VN516-500</t>
+  </si>
+  <si>
     <t>elc_wof_003</t>
   </si>
   <si>
     <t>e_w548970103-220,e_w548970101-220,e_w827889600-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_w548752026-220,e_w548723124-220,e_w1273948690-220,e_w1273948701-220,e_VN1016-500,e_w548717060-500,e_VN1003-500,e_VN988-220,e_w549038673-220,e_VN999-500</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w549400051-220,e_w1374565925-220</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_w1272088369-220,e_w549400051-220,e_w1258175914-220</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_VN516-500,e_w1374565925-220</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w1272088369-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_VN1003-500,e_VN999-500,e_VN988-220,e_w1091686589-220</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_w401042494-220,e_VN516-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w548970101-220,e_w827889600-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_w630750798-220,e_w1320784083-500,e_VN410-220,e_w630750798-500,e_w1183902227-500</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_VN1228-220,e_w548752026-220,e_w548723124-220,e_w1273948701-220,e_w548717060-500,e_VN1003-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w1273527149-220,e_VN836-220,e_w1273255946-220,e_w549197475-220,e_w549296358-220,e_w1272088369-220,e_w1376430795-500</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w1272088369-220,e_w1258175914-220,e_w549400051-220</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w827889600-500,e_VN1228-220,e_VN1145-220</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_w436002389-220,e_VN470-500,e_w1183902227-500,e_w401042494-220,e_VN471-500,e_w1087113517-220,e_VN516-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_w750907640-220,e_w1044469623-220,e_w715041211-220</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_w715041211-220,e_w1245195233-220</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -8279,7 +8279,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0088EF8-6BF3-4903-81BA-3750E1051D66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1234E75D-A055-4E87-9954-15C6E2EA38CF}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8559,10 +8559,10 @@
         <v>364</v>
       </c>
       <c r="AO11">
-        <v>0.9975164323387431</v>
+        <v>0.99796388855873064</v>
       </c>
       <c r="AP11">
-        <v>45.532073789710303</v>
+        <v>37.328709756605285</v>
       </c>
       <c r="AR11" t="s">
         <v>252</v>
@@ -8595,10 +8595,10 @@
         <v>442</v>
       </c>
       <c r="BC11">
-        <v>0.99660067059502699</v>
+        <v>0.98791946624258509</v>
       </c>
       <c r="BD11">
-        <v>62.321039091172274</v>
+        <v>221.4764522192738</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8705,10 +8705,10 @@
         <v>366</v>
       </c>
       <c r="AO12">
-        <v>0.99938105508849573</v>
+        <v>0.995847998099891</v>
       </c>
       <c r="AP12">
-        <v>11.34732337757792</v>
+        <v>76.120034835332021</v>
       </c>
       <c r="AR12" t="s">
         <v>252</v>
@@ -8741,10 +8741,10 @@
         <v>444</v>
       </c>
       <c r="BC12">
-        <v>0.98791946624258509</v>
+        <v>0.99509603189170837</v>
       </c>
       <c r="BD12">
-        <v>221.4764522192738</v>
+        <v>89.90608198534612</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8851,10 +8851,10 @@
         <v>368</v>
       </c>
       <c r="AO13">
-        <v>0.99881597306370296</v>
+        <v>0.99837166789655962</v>
       </c>
       <c r="AP13">
-        <v>21.707160498778528</v>
+        <v>29.852755229741184</v>
       </c>
       <c r="AR13" t="s">
         <v>252</v>
@@ -8887,10 +8887,10 @@
         <v>446</v>
       </c>
       <c r="BC13">
-        <v>0.99509603189170837</v>
+        <v>0.99122511500292365</v>
       </c>
       <c r="BD13">
-        <v>89.90608198534612</v>
+        <v>160.87289161306575</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8997,10 +8997,10 @@
         <v>370</v>
       </c>
       <c r="AO14">
-        <v>0.9982523129285531</v>
+        <v>0.99766805126871516</v>
       </c>
       <c r="AP14">
-        <v>32.040929643194062</v>
+        <v>42.752393406888629</v>
       </c>
       <c r="AR14" t="s">
         <v>252</v>
@@ -9033,10 +9033,10 @@
         <v>448</v>
       </c>
       <c r="BC14">
-        <v>0.99560758626248369</v>
+        <v>0.98952018191105418</v>
       </c>
       <c r="BD14">
-        <v>80.527585187798735</v>
+        <v>192.12999829733911</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9143,10 +9143,10 @@
         <v>372</v>
       </c>
       <c r="AO15">
-        <v>0.99766805126871516</v>
+        <v>0.9982523129285531</v>
       </c>
       <c r="AP15">
-        <v>42.752393406888629</v>
+        <v>32.040929643194062</v>
       </c>
       <c r="AR15" t="s">
         <v>252</v>
@@ -9179,10 +9179,10 @@
         <v>450</v>
       </c>
       <c r="BC15">
-        <v>0.98877515176124608</v>
+        <v>0.98985969450990097</v>
       </c>
       <c r="BD15">
-        <v>205.78888437715531</v>
+        <v>185.9056006518154</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9289,10 +9289,10 @@
         <v>374</v>
       </c>
       <c r="AO16">
-        <v>0.99894245995613196</v>
+        <v>0.99897336142834126</v>
       </c>
       <c r="AP16">
-        <v>19.388234137580387</v>
+        <v>18.821707147077909</v>
       </c>
       <c r="AR16" t="s">
         <v>252</v>
@@ -9325,10 +9325,10 @@
         <v>452</v>
       </c>
       <c r="BC16">
-        <v>0.99122511500292365</v>
+        <v>0.99345827826480626</v>
       </c>
       <c r="BD16">
-        <v>160.87289161306575</v>
+        <v>119.93156514521847</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9393,16 +9393,16 @@
         <v>267</v>
       </c>
       <c r="Y17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Z17" t="s">
         <v>311</v>
       </c>
       <c r="AA17">
-        <v>0.99841532396070098</v>
+        <v>0.99897010067703429</v>
       </c>
       <c r="AB17">
-        <v>29.052394053816059</v>
+        <v>18.881487587705607</v>
       </c>
       <c r="AD17" t="s">
         <v>252</v>
@@ -9435,10 +9435,10 @@
         <v>376</v>
       </c>
       <c r="AO17">
-        <v>0.99926426412261371</v>
+        <v>0.99906402131845495</v>
       </c>
       <c r="AP17">
-        <v>13.488491085415317</v>
+        <v>17.15960916165827</v>
       </c>
       <c r="AR17" t="s">
         <v>252</v>
@@ -9471,10 +9471,10 @@
         <v>454</v>
       </c>
       <c r="BC17">
-        <v>0.98952018191105418</v>
+        <v>0.99660067059502699</v>
       </c>
       <c r="BD17">
-        <v>192.12999829733911</v>
+        <v>62.321039091172274</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9539,16 +9539,16 @@
         <v>269</v>
       </c>
       <c r="Y18" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="Z18" t="s">
         <v>312</v>
       </c>
       <c r="AA18">
-        <v>0.99748798960410945</v>
+        <v>0.99790242535065354</v>
       </c>
       <c r="AB18">
-        <v>46.05352392465965</v>
+        <v>38.455535238019358</v>
       </c>
       <c r="AD18" t="s">
         <v>252</v>
@@ -9581,10 +9581,10 @@
         <v>378</v>
       </c>
       <c r="AO18">
-        <v>0.99911920301541846</v>
+        <v>0.99898558640402924</v>
       </c>
       <c r="AP18">
-        <v>16.147944717327473</v>
+        <v>18.597582592797586</v>
       </c>
       <c r="AR18" t="s">
         <v>252</v>
@@ -9614,13 +9614,13 @@
         <v>455</v>
       </c>
       <c r="BB18" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="BC18">
-        <v>0.98985969450990097</v>
+        <v>0.98389971341016413</v>
       </c>
       <c r="BD18">
-        <v>185.9056006518154</v>
+        <v>295.17192081365857</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9685,16 +9685,16 @@
         <v>271</v>
       </c>
       <c r="Y19" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="Z19" t="s">
         <v>313</v>
       </c>
       <c r="AA19">
-        <v>0.99853082183379016</v>
+        <v>0.99922833574773007</v>
       </c>
       <c r="AB19">
-        <v>26.934933047180987</v>
+        <v>14.14717795828226</v>
       </c>
       <c r="AD19" t="s">
         <v>252</v>
@@ -9727,10 +9727,10 @@
         <v>380</v>
       </c>
       <c r="AO19">
-        <v>0.99796388855873064</v>
+        <v>0.99938105508849573</v>
       </c>
       <c r="AP19">
-        <v>37.328709756605285</v>
+        <v>11.34732337757792</v>
       </c>
       <c r="AR19" t="s">
         <v>252</v>
@@ -9757,16 +9757,16 @@
         <v>413</v>
       </c>
       <c r="BA19" t="s">
+        <v>456</v>
+      </c>
+      <c r="BB19" t="s">
         <v>457</v>
       </c>
-      <c r="BB19" t="s">
-        <v>444</v>
-      </c>
       <c r="BC19">
-        <v>0.98389971341016413</v>
+        <v>0.99068186135163905</v>
       </c>
       <c r="BD19">
-        <v>295.17192081365857</v>
+        <v>170.83254188661647</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9831,16 +9831,16 @@
         <v>273</v>
       </c>
       <c r="Y20" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="Z20" t="s">
         <v>314</v>
       </c>
       <c r="AA20">
-        <v>0.99886029773300145</v>
+        <v>0.99930751773166338</v>
       </c>
       <c r="AB20">
-        <v>20.894541561640985</v>
+        <v>12.695508252837362</v>
       </c>
       <c r="AD20" t="s">
         <v>252</v>
@@ -9873,10 +9873,10 @@
         <v>382</v>
       </c>
       <c r="AO20">
-        <v>0.995847998099891</v>
+        <v>0.99844423111858249</v>
       </c>
       <c r="AP20">
-        <v>76.120034835332021</v>
+        <v>28.522429492654361</v>
       </c>
       <c r="AR20" t="s">
         <v>252</v>
@@ -9909,10 +9909,10 @@
         <v>459</v>
       </c>
       <c r="BC20">
-        <v>0.99068186135163905</v>
+        <v>0.98020101972536366</v>
       </c>
       <c r="BD20">
-        <v>170.83254188661647</v>
+        <v>362.98130503499954</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9977,16 +9977,16 @@
         <v>275</v>
       </c>
       <c r="Y21" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="Z21" t="s">
         <v>315</v>
       </c>
       <c r="AA21">
-        <v>0.99881634769332572</v>
+        <v>0.99544370356555212</v>
       </c>
       <c r="AB21">
-        <v>21.700292289029083</v>
+        <v>83.53210129821079</v>
       </c>
       <c r="AD21" t="s">
         <v>252</v>
@@ -10019,10 +10019,10 @@
         <v>384</v>
       </c>
       <c r="AO21">
-        <v>0.99837166789655962</v>
+        <v>0.99887560286820065</v>
       </c>
       <c r="AP21">
-        <v>29.852755229741184</v>
+        <v>20.613947416322183</v>
       </c>
       <c r="AR21" t="s">
         <v>252</v>
@@ -10055,10 +10055,10 @@
         <v>461</v>
       </c>
       <c r="BC21">
-        <v>0.98020101972536366</v>
+        <v>0.97141625641711749</v>
       </c>
       <c r="BD21">
-        <v>362.98130503499954</v>
+        <v>524.03529901951276</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10123,16 +10123,16 @@
         <v>277</v>
       </c>
       <c r="Y22" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="Z22" t="s">
         <v>316</v>
       </c>
       <c r="AA22">
-        <v>0.99902825268538287</v>
+        <v>0.99874244650354715</v>
       </c>
       <c r="AB22">
-        <v>17.815367434646582</v>
+        <v>23.055147434969136</v>
       </c>
       <c r="AD22" t="s">
         <v>252</v>
@@ -10165,10 +10165,10 @@
         <v>386</v>
       </c>
       <c r="AO22">
-        <v>0.99897336142834126</v>
+        <v>0.99926426412261371</v>
       </c>
       <c r="AP22">
-        <v>18.821707147077909</v>
+        <v>13.488491085415317</v>
       </c>
       <c r="AR22" t="s">
         <v>252</v>
@@ -10201,10 +10201,10 @@
         <v>463</v>
       </c>
       <c r="BC22">
-        <v>0.97141625641711749</v>
+        <v>0.98009770506351668</v>
       </c>
       <c r="BD22">
-        <v>524.03529901951276</v>
+        <v>364.87540716886002</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10269,16 +10269,16 @@
         <v>279</v>
       </c>
       <c r="Y23" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Z23" t="s">
         <v>317</v>
       </c>
       <c r="AA23">
-        <v>0.99748113422069817</v>
+        <v>0.99853654721508034</v>
       </c>
       <c r="AB23">
-        <v>46.179205953867658</v>
+        <v>26.829967723528117</v>
       </c>
       <c r="AD23" t="s">
         <v>252</v>
@@ -10311,10 +10311,10 @@
         <v>388</v>
       </c>
       <c r="AO23">
-        <v>0.99906402131845495</v>
+        <v>0.99911920301541846</v>
       </c>
       <c r="AP23">
-        <v>17.15960916165827</v>
+        <v>16.147944717327473</v>
       </c>
       <c r="AR23" t="s">
         <v>252</v>
@@ -10347,10 +10347,10 @@
         <v>465</v>
       </c>
       <c r="BC23">
-        <v>0.99497940415328234</v>
+        <v>0.9969294297150163</v>
       </c>
       <c r="BD23">
-        <v>92.044257189823469</v>
+        <v>56.2937885580344</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10415,16 +10415,16 @@
         <v>281</v>
       </c>
       <c r="Y24" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="Z24" t="s">
         <v>318</v>
       </c>
       <c r="AA24">
-        <v>0.9968034818648015</v>
+        <v>0.99908330527279288</v>
       </c>
       <c r="AB24">
-        <v>58.602832478639002</v>
+        <v>16.806069998796339</v>
       </c>
       <c r="AD24" t="s">
         <v>252</v>
@@ -10457,10 +10457,10 @@
         <v>390</v>
       </c>
       <c r="AO24">
-        <v>0.99907918970282927</v>
+        <v>0.9975164323387431</v>
       </c>
       <c r="AP24">
-        <v>16.881522114796713</v>
+        <v>45.532073789710303</v>
       </c>
       <c r="AR24" t="s">
         <v>252</v>
@@ -10493,10 +10493,10 @@
         <v>467</v>
       </c>
       <c r="BC24">
-        <v>0.97765588244922996</v>
+        <v>0.99534342454901092</v>
       </c>
       <c r="BD24">
-        <v>409.64215509745077</v>
+        <v>85.370549934800536</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10561,16 +10561,16 @@
         <v>283</v>
       </c>
       <c r="Y25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s">
         <v>319</v>
       </c>
       <c r="AA25">
-        <v>0.99544314722299798</v>
+        <v>0.99925831158204348</v>
       </c>
       <c r="AB25">
-        <v>83.542300911704686</v>
+        <v>13.597620995868882</v>
       </c>
       <c r="AD25" t="s">
         <v>252</v>
@@ -10603,10 +10603,10 @@
         <v>392</v>
       </c>
       <c r="AO25">
-        <v>0.99898558640402924</v>
+        <v>0.99894245995613196</v>
       </c>
       <c r="AP25">
-        <v>18.597582592797586</v>
+        <v>19.388234137580387</v>
       </c>
       <c r="AR25" t="s">
         <v>252</v>
@@ -10639,10 +10639,10 @@
         <v>469</v>
       </c>
       <c r="BC25">
-        <v>0.99345827826480626</v>
+        <v>0.99497940415328234</v>
       </c>
       <c r="BD25">
-        <v>119.93156514521847</v>
+        <v>92.044257189823469</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10707,16 +10707,16 @@
         <v>285</v>
       </c>
       <c r="Y26" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Z26" t="s">
         <v>320</v>
       </c>
       <c r="AA26">
-        <v>0.99790242535065354</v>
+        <v>0.99544314722299798</v>
       </c>
       <c r="AB26">
-        <v>38.455535238019358</v>
+        <v>83.542300911704686</v>
       </c>
       <c r="AD26" t="s">
         <v>252</v>
@@ -10749,10 +10749,10 @@
         <v>394</v>
       </c>
       <c r="AO26">
-        <v>0.99887560286820065</v>
+        <v>0.99907918970282927</v>
       </c>
       <c r="AP26">
-        <v>20.613947416322183</v>
+        <v>16.881522114796713</v>
       </c>
       <c r="AR26" t="s">
         <v>252</v>
@@ -10785,10 +10785,10 @@
         <v>471</v>
       </c>
       <c r="BC26">
-        <v>0.98009770506351668</v>
+        <v>0.99160116355990502</v>
       </c>
       <c r="BD26">
-        <v>364.87540716886002</v>
+        <v>153.97866806840764</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10853,16 +10853,16 @@
         <v>287</v>
       </c>
       <c r="Y27" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Z27" t="s">
         <v>321</v>
       </c>
       <c r="AA27">
-        <v>0.99922833574773007</v>
+        <v>0.99881634769332572</v>
       </c>
       <c r="AB27">
-        <v>14.14717795828226</v>
+        <v>21.700292289029083</v>
       </c>
       <c r="AD27" t="s">
         <v>252</v>
@@ -10895,10 +10895,10 @@
         <v>396</v>
       </c>
       <c r="AO27">
-        <v>0.99844423111858249</v>
+        <v>0.99881597306370296</v>
       </c>
       <c r="AP27">
-        <v>28.522429492654361</v>
+        <v>21.707160498778528</v>
       </c>
       <c r="AR27" t="s">
         <v>252</v>
@@ -10931,10 +10931,10 @@
         <v>473</v>
       </c>
       <c r="BC27">
-        <v>0.9969294297150163</v>
+        <v>0.99255179421932938</v>
       </c>
       <c r="BD27">
-        <v>56.2937885580344</v>
+        <v>136.55043931229389</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10999,16 +10999,16 @@
         <v>289</v>
       </c>
       <c r="Y28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z28" t="s">
         <v>322</v>
       </c>
       <c r="AA28">
-        <v>0.99897010067703429</v>
+        <v>0.99902825268538287</v>
       </c>
       <c r="AB28">
-        <v>18.881487587705607</v>
+        <v>17.815367434646582</v>
       </c>
       <c r="AR28" t="s">
         <v>252</v>
@@ -11041,10 +11041,10 @@
         <v>475</v>
       </c>
       <c r="BC28">
-        <v>0.99534342454901092</v>
+        <v>0.99560758626248369</v>
       </c>
       <c r="BD28">
-        <v>85.370549934800536</v>
+        <v>80.527585187798735</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11109,16 +11109,16 @@
         <v>291</v>
       </c>
       <c r="Y29" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="Z29" t="s">
         <v>323</v>
       </c>
       <c r="AA29">
-        <v>0.99930751773166338</v>
+        <v>0.99841532396070098</v>
       </c>
       <c r="AB29">
-        <v>12.695508252837362</v>
+        <v>29.052394053816059</v>
       </c>
       <c r="AR29" t="s">
         <v>252</v>
@@ -11151,10 +11151,10 @@
         <v>477</v>
       </c>
       <c r="BC29">
-        <v>0.98627052110774238</v>
+        <v>0.97765588244922996</v>
       </c>
       <c r="BD29">
-        <v>251.70711302472259</v>
+        <v>409.64215509745077</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11219,16 +11219,16 @@
         <v>293</v>
       </c>
       <c r="Y30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Z30" t="s">
         <v>324</v>
       </c>
       <c r="AA30">
-        <v>0.99544370356555212</v>
+        <v>0.99748798960410945</v>
       </c>
       <c r="AB30">
-        <v>83.53210129821079</v>
+        <v>46.05352392465965</v>
       </c>
       <c r="AR30" t="s">
         <v>252</v>
@@ -11261,10 +11261,10 @@
         <v>479</v>
       </c>
       <c r="BC30">
-        <v>0.99278784076394344</v>
+        <v>0.98627052110774238</v>
       </c>
       <c r="BD30">
-        <v>132.22291932770449</v>
+        <v>251.70711302472259</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11329,16 +11329,16 @@
         <v>295</v>
       </c>
       <c r="Y31" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="Z31" t="s">
         <v>325</v>
       </c>
       <c r="AA31">
-        <v>0.99874244650354715</v>
+        <v>0.99853082183379016</v>
       </c>
       <c r="AB31">
-        <v>23.055147434969136</v>
+        <v>26.934933047180987</v>
       </c>
       <c r="AR31" t="s">
         <v>252</v>
@@ -11371,10 +11371,10 @@
         <v>481</v>
       </c>
       <c r="BC31">
-        <v>0.99160116355990502</v>
+        <v>0.99278784076394344</v>
       </c>
       <c r="BD31">
-        <v>153.97866806840764</v>
+        <v>132.22291932770449</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11439,16 +11439,16 @@
         <v>297</v>
       </c>
       <c r="Y32" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="Z32" t="s">
         <v>326</v>
       </c>
       <c r="AA32">
-        <v>0.99853654721508034</v>
+        <v>0.99886029773300145</v>
       </c>
       <c r="AB32">
-        <v>26.829967723528117</v>
+        <v>20.894541561640985</v>
       </c>
       <c r="AR32" t="s">
         <v>252</v>
@@ -11481,10 +11481,10 @@
         <v>483</v>
       </c>
       <c r="BC32">
-        <v>0.99255179421932938</v>
+        <v>0.98877515176124608</v>
       </c>
       <c r="BD32">
-        <v>136.55043931229389</v>
+        <v>205.78888437715531</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -11549,16 +11549,16 @@
         <v>299</v>
       </c>
       <c r="Y33" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="Z33" t="s">
         <v>327</v>
       </c>
       <c r="AA33">
-        <v>0.99908330527279288</v>
+        <v>0.99748113422069817</v>
       </c>
       <c r="AB33">
-        <v>16.806069998796339</v>
+        <v>46.179205953867658</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -11623,16 +11623,16 @@
         <v>301</v>
       </c>
       <c r="Y34" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Z34" t="s">
         <v>328</v>
       </c>
       <c r="AA34">
-        <v>0.99925831158204348</v>
+        <v>0.9968034818648015</v>
       </c>
       <c r="AB34">
-        <v>13.597620995868882</v>
+        <v>58.602832478639002</v>
       </c>
     </row>
   </sheetData>
@@ -11641,7 +11641,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6F5AF5-AE10-4B03-AB82-BBEF6D72383B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAA16333-B445-4DF9-AB12-1E3CFF350AEC}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11753,7 +11753,7 @@
         <v>484</v>
       </c>
       <c r="K11" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="L11">
         <v>9.9561879268440521</v>
@@ -11786,7 +11786,7 @@
         <v>518</v>
       </c>
       <c r="X11" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="Y11">
         <v>5.7030000000000003</v>
@@ -11821,7 +11821,7 @@
         <v>486</v>
       </c>
       <c r="K12" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="L12">
         <v>15.610469208056319</v>
@@ -11854,7 +11854,7 @@
         <v>520</v>
       </c>
       <c r="X12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Y12">
         <v>3.2370000000000001</v>
@@ -11889,7 +11889,7 @@
         <v>488</v>
       </c>
       <c r="K13" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L13">
         <v>38.93604588989777</v>
@@ -11922,7 +11922,7 @@
         <v>522</v>
       </c>
       <c r="X13" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="Y13">
         <v>0.73950000000000005</v>
@@ -11957,7 +11957,7 @@
         <v>490</v>
       </c>
       <c r="K14" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="L14">
         <v>3.4061833906252343</v>
@@ -11990,7 +11990,7 @@
         <v>524</v>
       </c>
       <c r="X14" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="Y14">
         <v>17.418749999999999</v>
@@ -12025,7 +12025,7 @@
         <v>492</v>
       </c>
       <c r="K15" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="L15">
         <v>10.05531955531686</v>
@@ -12058,7 +12058,7 @@
         <v>526</v>
       </c>
       <c r="X15" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="Y15">
         <v>75.501750000000001</v>
@@ -12093,7 +12093,7 @@
         <v>494</v>
       </c>
       <c r="K16" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="L16">
         <v>11.000319473014851</v>
@@ -12126,7 +12126,7 @@
         <v>528</v>
       </c>
       <c r="X16" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="Y16">
         <v>26.099250000000001</v>
@@ -12161,7 +12161,7 @@
         <v>496</v>
       </c>
       <c r="K17" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="L17">
         <v>1.9758785540112649</v>
@@ -12194,7 +12194,7 @@
         <v>530</v>
       </c>
       <c r="X17" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Y17">
         <v>6.7657499999999997</v>
@@ -12229,7 +12229,7 @@
         <v>498</v>
       </c>
       <c r="K18" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="L18">
         <v>10.302711276720984</v>
@@ -12262,7 +12262,7 @@
         <v>532</v>
       </c>
       <c r="X18" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="Y18">
         <v>18.204750000000001</v>
@@ -12297,7 +12297,7 @@
         <v>500</v>
       </c>
       <c r="K19" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="L19">
         <v>21.084725957939643</v>
@@ -12330,7 +12330,7 @@
         <v>534</v>
       </c>
       <c r="X19" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="Y19">
         <v>53.964750000000002</v>
@@ -12365,7 +12365,7 @@
         <v>502</v>
       </c>
       <c r="K20" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L20">
         <v>7.8234985450080243</v>
@@ -12398,7 +12398,7 @@
         <v>536</v>
       </c>
       <c r="X20" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="Y20">
         <v>32.474249999999998</v>
@@ -12433,7 +12433,7 @@
         <v>504</v>
       </c>
       <c r="K21" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="L21">
         <v>35.48135454794123</v>
@@ -12466,7 +12466,7 @@
         <v>538</v>
       </c>
       <c r="X21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="Y21">
         <v>24.771750000000001</v>
@@ -12501,7 +12501,7 @@
         <v>506</v>
       </c>
       <c r="K22" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="L22">
         <v>31.11916467188631</v>
@@ -12534,7 +12534,7 @@
         <v>540</v>
       </c>
       <c r="X22" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="Y22">
         <v>34.518000000000001</v>
@@ -12569,7 +12569,7 @@
         <v>508</v>
       </c>
       <c r="K23" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="L23">
         <v>4.5001608244833662</v>
@@ -12602,7 +12602,7 @@
         <v>542</v>
       </c>
       <c r="X23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="Y23">
         <v>13.3995</v>
@@ -12637,7 +12637,7 @@
         <v>510</v>
       </c>
       <c r="K24" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L24">
         <v>9.5500952124569967</v>
@@ -12670,7 +12670,7 @@
         <v>544</v>
       </c>
       <c r="X24" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="Y24">
         <v>38.413499999999999</v>
@@ -12705,7 +12705,7 @@
         <v>512</v>
       </c>
       <c r="K25" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="L25">
         <v>5.3426370365388722</v>
@@ -12738,7 +12738,7 @@
         <v>546</v>
       </c>
       <c r="X25" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="Y25">
         <v>15.254250000000001</v>
@@ -12773,7 +12773,7 @@
         <v>514</v>
       </c>
       <c r="K26" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="L26">
         <v>1.0928295776667281</v>
@@ -12806,7 +12806,7 @@
         <v>548</v>
       </c>
       <c r="X26" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Y26">
         <v>16.820250000000001</v>
@@ -12841,7 +12841,7 @@
         <v>516</v>
       </c>
       <c r="K27" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="L27">
         <v>0.94607061901700107</v>
@@ -12874,7 +12874,7 @@
         <v>550</v>
       </c>
       <c r="X27" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Y27">
         <v>32.364750000000001</v>
@@ -12909,7 +12909,7 @@
         <v>552</v>
       </c>
       <c r="X28" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="Y28">
         <v>20.224499999999999</v>
@@ -12944,7 +12944,7 @@
         <v>554</v>
       </c>
       <c r="X29" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="Y29">
         <v>13.347</v>
@@ -12979,7 +12979,7 @@
         <v>556</v>
       </c>
       <c r="X30" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="Y30">
         <v>3.7177500000000001</v>
@@ -13014,7 +13014,7 @@
         <v>558</v>
       </c>
       <c r="X31" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="Y31">
         <v>9.6434999999999995</v>
@@ -13049,7 +13049,7 @@
         <v>560</v>
       </c>
       <c r="X32" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Y32">
         <v>38.509500000000003</v>
@@ -13064,7 +13064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42102259-BD5B-4C56-9C54-94497EB7F7B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E45426F-C74A-49B9-863A-626776DC7C7C}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14881,7 +14881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF37CA50-39BE-41DD-8D4E-E2B6A90143A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE249A9-547A-4EB0-986C-7F9C8DCC8880}">
   <dimension ref="B2:M187"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
